--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>76.61487579345703</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78.18000030517578</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.56512451171875</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.001949994383836</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.088262413885345</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>78.26858520507812</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>76.759712,76.770569,76.755997,76.787109,76.816147,76.810867,76.811211,76.783501,76.803978,76.798973,76.794113,76.775909,76.769608,76.753616,76.753044,76.703629,76.735985,76.734779,76.705536,76.687752,76.656242,76.654778,76.655052,76.614876</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>76.430000,75.849998,75.570000,76.150002,76.080002,76.400002,76.279999,77.070000,76.669998,76.209999,76.059998,77.720001,77.599998,77.680000,77.599998,77.570000,77.820000,77.699997,77.389999,77.790001,78.070000,77.779999,77.980003,78.180000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.329712,0.920571,1.185997,0.637107,0.736145,0.410865,0.531212,0.286499,0.133980,0.588974,0.734115,0.944092,0.830390,0.926384,0.846954,0.866371,1.084015,0.965218,0.684463,1.102249,1.413758,1.125221,1.324951,1.565124</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.431390,1.213672,1.569402,0.836648,0.967594,0.537782,0.696398,0.371738,0.174749,0.772830,0.965179,1.214735,1.070091,1.192565,1.091436,1.116889,1.392977,1.242237,0.884434,1.416954,1.810885,1.446671,1.699091,2.001950</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.088262413885345</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>76.709175,76.715881,76.732948,76.757561,76.754478,76.664909,76.770416,76.830750,76.650696,76.768181,76.679825,76.669121,76.659256,76.671181,76.635681,76.698196,76.678894,76.554985,76.576996,76.656197,76.576530,76.615540,76.473030,76.437279</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>76.390450,76.337372,76.243942,76.257675,76.228004,76.144905,76.113068,76.062424,76.071106,75.990929,75.930481,75.914970,75.888695,75.771042,75.734802,75.666084,75.662964,75.615974,75.539291,75.464661,75.422432,75.329163,75.347191,75.281525</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>78.172722,78.146324,78.147720,78.186607,78.225845,78.209869,78.237602,78.269958,78.295815,78.274231,78.334183,78.330910,78.320221,78.288460,78.321182,78.277306,78.332779,78.299957,78.319077,78.289505,78.261734,78.267838,78.278076,78.268585</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>78.047417,78.127869,78.189301,78.113541,78.161873,78.107971,78.186882,78.367950,78.050385,78.305710,78.317795,78.168320,78.179276,78.165298,78.183434,78.306664,78.227974,78.136459,78.143112,78.225433,78.182190,78.289192,78.137497,78.075493</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>77.500122,77.321251,77.232330,77.168533,77.175964,77.046906,77.024948,76.963211,77.013596,76.856239,76.928596,76.727402,76.755241,76.549347,76.503662,76.388260,76.363617,76.325661,76.154144,76.009056,75.989128,75.931099,75.904839,75.818878</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>77.763290,77.643387,77.586998,77.594254,77.586388,77.481140,77.493973,77.481857,77.525719,77.411850,77.432961,77.403595,77.368149,77.229492,77.194550,77.133972,77.121437,77.066414,77.000664,76.950699,76.888062,76.794579,76.826447,76.759056</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>78.26858520507812</v>
+      </c>
+      <c r="G3" t="n">
+        <v>78.11000061035156</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1585845947265625</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.203027260897942</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3321249365267397</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:47</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>78.16097259521484</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>78.172722,78.146324,78.147720,78.186607,78.225845,78.209869,78.237602,78.269958,78.295815,78.274231,78.334183,78.330910,78.320221,78.288460,78.321182,78.277306,78.332779,78.299957,78.319077,78.289505,78.261734,78.267838,78.278076,78.268585</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78.080002,78.389999,78.610001,78.510002,78.300003,78.370003,78.160004,78.320000,78.459999,78.540001,77.940002,78.099998,78.160004,77.669998,77.820000,77.820000,77.879997,77.980003,77.949997,78.040001,78.430000,78.300003,78.080002,78.110001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.092720,0.243675,0.462281,0.323395,0.074158,0.160134,0.077598,0.050042,0.164184,0.265770,0.394181,0.230912,0.160217,0.618462,0.501182,0.457306,0.452782,0.319954,0.369080,0.249504,0.168266,0.032165,0.198074,0.158584</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.118750,0.310850,0.588068,0.411916,0.094710,0.204330,0.099281,0.063894,0.209258,0.338388,0.505749,0.295661,0.204986,0.796269,0.644028,0.587646,0.581384,0.410302,0.473483,0.319713,0.214543,0.041079,0.253681,0.203027</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3321249365267397</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>78.047417,78.127869,78.189301,78.113541,78.161873,78.107971,78.186882,78.367950,78.050385,78.305710,78.317795,78.168320,78.179276,78.165298,78.183434,78.306664,78.227974,78.136459,78.143112,78.225433,78.182190,78.289192,78.137497,78.075493</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>77.763290,77.643387,77.586998,77.594254,77.586388,77.481140,77.493973,77.481857,77.525719,77.411850,77.432961,77.403595,77.368149,77.229492,77.194550,77.133972,77.121437,77.066414,77.000664,76.950699,76.888062,76.794579,76.826447,76.759056</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:47</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>78.111465,78.093277,78.106064,78.120132,78.111588,78.091995,78.061920,78.048782,78.109169,78.080124,78.062790,78.106583,78.098396,78.037964,78.088226,78.064545,78.115974,78.112900,78.096909,78.086021,78.084961,78.148407,78.164009,78.160973</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>78.024719,78.020752,78.138397,78.135429,78.015999,78.045914,77.973763,78.063873,77.983696,78.055321,78.050514,78.001297,77.901787,77.893845,77.961845,78.045532,78.022400,77.985153,77.974968,77.982430,77.998413,78.072830,78.082535,77.976669</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>77.674629,77.586517,77.498764,77.370522,77.350914,77.211899,77.087158,76.954300,77.107880,76.951042,76.963211,76.770103,76.840836,76.586014,76.576660,76.488960,76.469864,76.445328,76.284378,76.154053,76.155624,76.112312,76.108780,76.031586</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>77.821472,77.779953,77.726555,77.705475,77.640854,77.535622,77.526527,77.440155,77.530266,77.411583,77.356606,77.404388,77.319298,77.169205,77.161789,77.121170,77.091354,77.051086,77.000031,76.922668,76.914978,76.877319,76.899490,76.821548</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>78.16097259521484</v>
+      </c>
+      <c r="G4" t="n">
+        <v>77.59999847412109</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.56097412109375</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7229048094386623</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5520519728065056</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:47</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77.50115203857422</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>78.111465,78.093277,78.106064,78.120132,78.111588,78.091995,78.061920,78.048782,78.109169,78.080124,78.062790,78.106583,78.098396,78.037964,78.088226,78.064545,78.115974,78.112900,78.096909,78.086021,78.084961,78.148407,78.164009,78.160973</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>78.019997,77.379997,77.250000,77.050003,77.379997,77.500000,77.620003,77.510002,77.180000,77.820000,77.849998,78.419998,78.550003,78.190002,77.720001,77.639999,77.769997,78.000000,77.989998,77.949997,78.230003,77.860001,77.730003,77.599998</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.091468,0.713280,0.856064,1.070129,0.731591,0.591995,0.441917,0.538780,0.929169,0.260124,0.212792,0.313415,0.451607,0.152038,0.368225,0.424546,0.345977,0.112900,0.106911,0.136024,0.145042,0.288406,0.434006,0.560975</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.117237,0.921788,1.108173,1.388876,0.945452,0.763865,0.569334,0.695110,1.203898,0.334264,0.273335,0.399662,0.574929,0.194447,0.473784,0.546813,0.444873,0.144744,0.137083,0.174502,0.185405,0.370417,0.558350,0.722905</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5520519728065056</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>78.024719,78.020752,78.138397,78.135429,78.015999,78.045914,77.973763,78.063873,77.983696,78.055321,78.050514,78.001297,77.901787,77.893845,77.961845,78.045532,78.022400,77.985153,77.974968,77.982430,77.998413,78.072830,78.082535,77.976669</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>77.821472,77.779953,77.726555,77.705475,77.640854,77.535622,77.526527,77.440155,77.530266,77.411583,77.356606,77.404388,77.319298,77.169205,77.161789,77.121170,77.091354,77.051086,77.000031,76.922668,76.914978,76.877319,76.899490,76.821548</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:47</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>77.538910,77.525612,77.525665,77.497932,77.505569,77.506622,77.522003,77.522469,77.577225,77.589653,77.604919,77.593842,77.586708,77.575920,77.584122,77.561928,77.586617,77.549408,77.506546,77.533844,77.509827,77.515106,77.528831,77.501152</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>77.541832,77.529434,77.562592,77.522324,77.519791,77.514572,77.513939,77.562408,77.581146,77.532600,77.672585,77.542961,77.557968,77.564110,77.544220,77.528893,77.498474,77.454216,77.462372,77.422539,77.475151,77.404121,77.512077,77.409607</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>77.051605,76.919739,76.824638,76.695152,76.600273,76.524254,76.479294,76.389648,76.467964,76.367752,76.360374,76.212646,76.197884,76.138336,76.045898,75.974564,75.956268,75.857574,75.630035,75.616913,75.554993,75.520195,75.503700,75.443863</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>77.249847,77.164261,77.072914,77.005455,76.951904,76.869904,76.869720,76.828926,76.936127,76.843765,76.805519,76.770050,76.723923,76.688805,76.654938,76.609711,76.612274,76.490311,76.423691,76.404999,76.350571,76.278168,76.302856,76.262367</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>77.50115203857422</v>
+      </c>
+      <c r="G5" t="n">
+        <v>75.86000061035156</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.641151428222656</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.163394957841209</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.420280076907534</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>75.63140869140625</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>77.538910,77.525612,77.525665,77.497932,77.505569,77.506622,77.522003,77.522469,77.577225,77.589653,77.604919,77.593842,77.586708,77.575920,77.584122,77.561928,77.586617,77.549408,77.506546,77.533844,77.509827,77.515106,77.528831,77.501152</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>77.470001,77.489998,77.540001,77.120003,77.430000,77.459999,77.709999,77.620003,76.889999,76.660004,76.379997,76.320000,75.930000,75.580002,75.730003,75.690002,76.070000,75.980003,76.129997,75.820000,75.779999,75.629997,75.470001,75.860001</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.068909,0.035614,0.014336,0.377929,0.075569,0.046623,0.187996,0.097534,0.687226,0.929649,1.224922,1.273842,1.656708,1.995918,1.854119,1.871926,1.516617,1.569405,1.376549,1.713844,1.729828,1.885109,2.058830,1.641151</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.088949,0.045960,0.018488,0.490053,0.097596,0.060190,0.241920,0.125655,0.893778,1.212691,1.603721,1.669081,2.181888,2.640802,2.448328,2.473148,1.993713,2.065550,1.808156,2.260412,2.282698,2.492541,2.728011,2.163395</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.420280076907534</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>77.541832,77.529434,77.562592,77.522324,77.519791,77.514572,77.513939,77.562408,77.581146,77.532600,77.672585,77.542961,77.557968,77.564110,77.544220,77.528893,77.498474,77.454216,77.462372,77.422539,77.475151,77.404121,77.512077,77.409607</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>77.249847,77.164261,77.072914,77.005455,76.951904,76.869904,76.869720,76.828926,76.936127,76.843765,76.805519,76.770050,76.723923,76.688805,76.654938,76.609711,76.612274,76.490311,76.423691,76.404999,76.350571,76.278168,76.302856,76.262367</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>75.822006,75.789055,75.784027,75.772873,75.792755,75.786461,75.795410,75.755875,75.770912,75.790131,75.761452,75.769119,75.741768,75.718185,75.689636,75.637573,75.652863,75.650284,75.636269,75.663269,75.624954,75.649811,75.628708,75.631409</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>75.773407,75.868698,75.771454,75.747269,75.786758,75.838593,75.842804,75.746887,75.816422,75.828644,75.807442,75.766693,75.817970,75.760071,75.774246,75.618866,75.673454,75.741264,75.786102,75.659470,75.676125,75.579887,75.680557,75.714447</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>75.221848,75.108978,75.023956,74.968529,74.930199,74.918015,74.849365,74.717361,74.715179,74.621582,74.550568,74.428802,74.353668,74.267960,74.216003,74.084724,74.051605,73.967239,73.786285,73.753990,73.681030,73.670242,73.625809,73.599823</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>75.432091,75.354858,75.292023,75.264053,75.261490,75.214996,75.206879,75.120415,75.158890,75.050377,74.947571,74.970299,74.885406,74.814087,74.806671,74.686569,74.708290,74.560417,74.533768,74.505241,74.438881,74.427963,74.423218,74.392700</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>75.63140869140625</v>
+      </c>
+      <c r="G6" t="n">
+        <v>74.18000030517578</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.451408386230469</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.956603370530317</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.62905562821662</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>74.23358917236328</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>75.822006,75.789055,75.784027,75.772873,75.792755,75.786461,75.795410,75.755875,75.770912,75.790131,75.761452,75.769119,75.741768,75.718185,75.689636,75.637573,75.652863,75.650284,75.636269,75.663269,75.624954,75.649811,75.628708,75.631409</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>75.610001,75.730003,75.790001,76.029999,75.720001,75.570000,75.430000,75.139999,74.800003,74.129997,73.980003,73.959999,73.839996,73.980003,73.910004,73.870003,73.709999,73.559998,73.870003,73.900002,74.070000,74.059998,74.050003,74.180000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.212005,0.059052,0.005974,0.257126,0.072754,0.216461,0.365410,0.615876,0.970909,1.660134,1.781449,1.809120,1.901772,1.738182,1.779632,1.767570,1.942864,2.090286,1.766266,1.763267,1.554954,1.589813,1.578705,1.451409</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.280393,0.077977,0.007882,0.338190,0.096083,0.286438,0.484435,0.819637,1.298007,2.239490,2.408014,2.446079,2.575531,2.349529,2.407837,2.392812,2.635821,2.841608,2.391047,2.386018,2.099304,2.146656,2.131944,1.956604</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.62905562821662</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>75.773407,75.868698,75.771454,75.747269,75.786758,75.838593,75.842804,75.746887,75.816422,75.828644,75.807442,75.766693,75.817970,75.760071,75.774246,75.618866,75.673454,75.741264,75.786102,75.659470,75.676125,75.579887,75.680557,75.714447</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>75.432091,75.354858,75.292023,75.264053,75.261490,75.214996,75.206879,75.120415,75.158890,75.050377,74.947571,74.970299,74.885406,74.814087,74.806671,74.686569,74.708290,74.560417,74.533768,74.505241,74.438881,74.427963,74.423218,74.392700</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>74.193764,74.220612,74.267349,74.250023,74.274818,74.296654,74.314957,74.300781,74.313896,74.320839,74.307190,74.263710,74.245300,74.245987,74.214401,74.200432,74.195831,74.212456,74.192238,74.230202,74.220879,74.236946,74.232483,74.233589</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>74.143929,74.293159,74.234131,74.222374,74.273254,74.369202,74.369019,74.328972,74.378494,74.411163,74.394142,74.293228,74.398575,74.330925,74.321259,74.304092,74.240234,74.356277,74.347275,74.324371,74.285767,74.226166,74.298943,74.342224</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>73.758316,73.698639,73.652641,73.598190,73.561951,73.563156,73.516556,73.392456,73.393723,73.278442,73.215462,73.047951,73.016068,72.981415,72.888496,72.801804,72.760712,72.718697,72.505630,72.519409,72.449219,72.449806,72.435043,72.436592</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>73.919724,73.906898,73.879143,73.845230,73.859184,73.848053,73.834213,73.781006,73.803696,73.654755,73.559799,73.555641,73.476898,73.452705,73.400269,73.328079,73.353806,73.211151,73.191193,73.183777,73.130112,73.136665,73.146721,73.130890</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>74.23358917236328</v>
+      </c>
+      <c r="G7" t="n">
+        <v>74.91999816894531</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6864089965820312</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9161892863827524</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4565128455780091</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:41:59</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>75.08407592773438</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>74.193764,74.220612,74.267349,74.250023,74.274818,74.296654,74.314957,74.300781,74.313896,74.320839,74.307190,74.263710,74.245300,74.245987,74.214401,74.200432,74.195831,74.212456,74.192238,74.230202,74.220879,74.236946,74.232483,74.233589</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>74.250000,73.910004,73.970001,73.730003,73.739998,73.930000,73.919998,73.860001,73.900002,73.910004,73.980003,74.110001,74.260002,74.400002,74.599998,74.510002,74.389999,74.400002,74.440002,74.339996,74.720001,74.760002,74.830002,74.919998</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.056236,0.310608,0.297348,0.520020,0.534820,0.366654,0.394959,0.440780,0.413894,0.410835,0.327187,0.153709,0.014702,0.154015,0.385597,0.309570,0.194168,0.187546,0.247764,0.109794,0.499122,0.523056,0.597519,0.686409</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.075739,0.420252,0.401984,0.705303,0.725278,0.495947,0.534306,0.596778,0.560074,0.555859,0.442264,0.207407,0.019798,0.207009,0.516887,0.415475,0.261014,0.252077,0.332838,0.147692,0.667990,0.699647,0.798502,0.916190</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4565128455780091</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>74.143929,74.293159,74.234131,74.222374,74.273254,74.369202,74.369019,74.328972,74.378494,74.411163,74.394142,74.293228,74.398575,74.330925,74.321259,74.304092,74.240234,74.356277,74.347275,74.324371,74.285767,74.226166,74.298943,74.342224</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>73.919724,73.906898,73.879143,73.845230,73.859184,73.848053,73.834213,73.781006,73.803696,73.654755,73.559799,73.555641,73.476898,73.452705,73.400269,73.328079,73.353806,73.211151,73.191193,73.183777,73.130112,73.136665,73.146721,73.130890</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:41:59</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>74.937439,74.985069,75.020111,75.011948,75.039360,75.052971,75.063660,75.072021,75.083313,75.085106,75.096291,75.082901,75.081360,75.098160,75.085510,75.053764,75.063644,75.048927,75.055779,75.069290,75.046745,75.063042,75.063950,75.084076</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>74.909271,74.979645,75.049255,75.002396,75.053314,75.082870,75.040504,75.130264,75.039406,75.177681,75.133682,75.031670,75.193733,75.157883,75.158890,75.200348,75.099045,75.105896,75.121605,75.152512,75.123245,75.109131,75.098602,75.142227</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>74.558960,74.531662,74.467865,74.408531,74.381088,74.358864,74.309784,74.265129,74.230652,74.155708,74.134354,74.034760,74.018219,73.977562,73.924706,73.856003,73.818626,73.794617,73.669655,73.644798,73.576538,73.549133,73.513092,73.482735</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>74.702057,74.702194,74.670418,74.639442,74.632111,74.624535,74.578987,74.559814,74.559235,74.486214,74.434212,74.460068,74.392273,74.381943,74.367348,74.322731,74.275681,74.219933,74.202324,74.180756,74.102959,74.089188,74.070068,74.065376</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>75.08407592773438</v>
+      </c>
+      <c r="G8" t="n">
+        <v>76.31999969482422</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.235923767089844</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.619396975932719</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6451974130356301</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>76.49929046630859</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>74.937439,74.985069,75.020111,75.011948,75.039360,75.052971,75.063660,75.072021,75.083313,75.085106,75.096291,75.082901,75.081360,75.098160,75.085510,75.053764,75.063644,75.048927,75.055779,75.069290,75.046745,75.063042,75.063950,75.084076</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>75.000000,74.959999,75.059998,74.820000,74.919998,75.010002,75.059998,74.889999,74.809998,74.870003,75.000000,75.430000,75.480003,75.320000,75.320000,75.279999,75.269997,75.589996,76.639999,76.690002,76.260002,76.449997,76.379997,76.320000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.062561,0.025070,0.039887,0.191948,0.119362,0.042969,0.003662,0.182022,0.273315,0.215103,0.096291,0.347099,0.398643,0.221840,0.234490,0.226235,0.206353,0.541069,1.584220,1.620712,1.213257,1.386955,1.316047,1.235924</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.083415,0.033444,0.053140,0.256547,0.159319,0.057284,0.004879,0.243052,0.365346,0.287302,0.128388,0.460161,0.528144,0.294530,0.311325,0.300524,0.274150,0.715795,2.067093,2.113329,1.590948,1.814199,1.723026,1.619397</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6451974130356301</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>74.909271,74.979645,75.049255,75.002396,75.053314,75.082870,75.040504,75.130264,75.039406,75.177681,75.133682,75.031670,75.193733,75.157883,75.158890,75.200348,75.099045,75.105896,75.121605,75.152512,75.123245,75.109131,75.098602,75.142227</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>74.702057,74.702194,74.670418,74.639442,74.632111,74.624535,74.578987,74.559814,74.559235,74.486214,74.434212,74.460068,74.392273,74.381943,74.367348,74.322731,74.275681,74.219933,74.202324,74.180756,74.102959,74.089188,74.070068,74.065376</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>76.327652,76.361496,76.405975,76.419937,76.454567,76.460190,76.467720,76.462029,76.486206,76.484558,76.489113,76.490555,76.511696,76.487328,76.507950,76.495941,76.527100,76.516998,76.537605,76.527115,76.489227,76.520226,76.495583,76.499290</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>76.298553,76.302620,76.363335,76.385315,76.440338,76.459534,76.401802,76.488342,76.444649,76.513901,76.472191,76.425552,76.532410,76.502090,76.505920,76.552826,76.542183,76.475433,76.482086,76.593643,76.493546,76.558365,76.525078,76.415070</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>75.764061,75.671555,75.598999,75.546585,75.486511,75.463188,75.413666,75.333099,75.329514,75.233643,75.209549,75.092377,75.146606,75.066086,75.041374,75.009773,74.984985,74.957962,74.839485,74.772453,74.696671,74.700325,74.649590,74.634460</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>75.985390,75.965393,75.921242,75.916321,75.865105,75.845909,75.837234,75.805840,75.806213,75.710663,75.622101,75.661728,75.643959,75.578506,75.582283,75.557579,75.562706,75.487854,75.481979,75.431320,75.347488,75.344498,75.330002,75.301880</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>76.49929046630859</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.26000213623047</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.239288330078125</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.421632863256698</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.450755003251329</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:37</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>73.65315246582031</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>76.327652,76.361496,76.405975,76.419937,76.454567,76.460190,76.467720,76.462029,76.486206,76.484558,76.489113,76.490555,76.511696,76.487328,76.507950,76.495941,76.527100,76.516998,76.537605,76.527115,76.489227,76.520226,76.495583,76.499290</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>76.250000,76.480003,76.650002,76.400002,76.239998,76.410004,76.540001,76.449997,76.779999,76.830002,75.389999,75.199997,75.879997,75.830002,75.529999,75.930000,75.910004,75.550003,74.000000,74.129997,73.660004,73.129997,73.300003,73.260002</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.077652,0.118507,0.244027,0.019935,0.214569,0.050186,0.072281,0.012032,0.293793,0.345444,1.099114,1.290558,0.631699,0.657326,0.977951,0.565941,0.617096,0.966995,2.537605,2.397118,2.829223,3.390229,3.195580,3.239288</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.101839,0.154952,0.318365,0.026094,0.281439,0.065680,0.094435,0.015738,0.382642,0.449621,1.457904,1.716168,0.832497,0.866842,1.294785,0.745345,0.812932,1.279940,3.429196,3.233668,3.840922,4.635893,4.359590,4.421632</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.450755003251329</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>76.298553,76.302620,76.363335,76.385315,76.440338,76.459534,76.401802,76.488342,76.444649,76.513901,76.472191,76.425552,76.532410,76.502090,76.505920,76.552826,76.542183,76.475433,76.482086,76.593643,76.493546,76.558365,76.525078,76.415070</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>75.985390,75.965393,75.921242,75.916321,75.865105,75.845909,75.837234,75.805840,75.806213,75.710663,75.622101,75.661728,75.643959,75.578506,75.582283,75.557579,75.562706,75.487854,75.481979,75.431320,75.347488,75.344498,75.330002,75.301880</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:37</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>73.186714,73.232224,73.274338,73.270493,73.320099,73.357849,73.394989,73.430939,73.446007,73.455170,73.519035,73.522224,73.549255,73.570251,73.587479,73.593971,73.588432,73.625237,73.615883,73.628433,73.621651,73.652809,73.629318,73.653152</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>73.159851,73.303680,73.310249,73.358154,73.353790,73.500229,73.534584,73.491158,73.560318,73.609573,73.571793,73.729156,73.746819,73.684586,73.769798,73.726685,73.780296,73.770935,73.747452,73.866379,73.833801,73.772415,73.736511,73.811424</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>72.461090,72.360458,72.252670,72.129715,72.104813,72.072540,72.015488,71.952347,71.937523,71.862564,71.912254,71.853798,71.903198,71.832321,71.853424,71.790123,71.770981,71.789612,71.672546,71.662277,71.604279,71.617233,71.603745,71.596672</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>72.728867,72.695641,72.599304,72.581985,72.547462,72.530640,72.532074,72.513199,72.482628,72.448204,72.438950,72.500519,72.448914,72.441086,72.477188,72.417831,72.381027,72.415474,72.395317,72.362129,72.339287,72.367569,72.338722,72.346069</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>73.65315246582031</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.37000274658203</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2831497192382812</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3859202789132673</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4065372169910906</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:34</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>73.74247741699219</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>73.186714,73.232224,73.274338,73.270493,73.320099,73.357849,73.394989,73.430939,73.446007,73.455170,73.519035,73.522224,73.549255,73.570251,73.587479,73.593971,73.588432,73.625237,73.615883,73.628433,73.621651,73.652809,73.629318,73.653152</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>73.139999,73.190002,73.370003,73.209999,73.269997,73.190002,73.080002,73.120003,73.300003,72.620003,73.309998,74.269997,74.349998,73.760002,73.790001,74.230003,73.940002,74.040001,73.339996,73.209999,73.690002,73.180000,73.589996,73.370003</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.046715,0.042222,0.095665,0.060494,0.050102,0.167847,0.314987,0.310936,0.146004,0.835167,0.209037,0.747773,0.800743,0.189751,0.202522,0.636032,0.351570,0.414764,0.275887,0.418434,0.068351,0.472809,0.039322,0.283149</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.063870,0.057688,0.130387,0.082631,0.068380,0.229330,0.431017,0.425241,0.199187,1.150051,0.285142,1.006830,1.076992,0.257255,0.274457,0.856840,0.475481,0.560189,0.376175,0.571553,0.092755,0.646090,0.053433,0.385920</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4065372169910906</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>73.159851,73.303680,73.310249,73.358154,73.353790,73.500229,73.534584,73.491158,73.560318,73.609573,73.571793,73.729156,73.746819,73.684586,73.769798,73.726685,73.780296,73.770935,73.747452,73.866379,73.833801,73.772415,73.736511,73.811424</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>72.728867,72.695641,72.599304,72.581985,72.547462,72.530640,72.532074,72.513199,72.482628,72.448204,72.438950,72.500519,72.448914,72.441086,72.477188,72.417831,72.381027,72.415474,72.395317,72.362129,72.339287,72.367569,72.338722,72.346069</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:34</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>73.331970,73.351738,73.418686,73.401054,73.455940,73.425568,73.463699,73.487244,73.473602,73.493118,73.548264,73.542336,73.594833,73.621361,73.623802,73.666016,73.646255,73.674683,73.692352,73.752510,73.681984,73.746750,73.740082,73.742477</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>73.403824,73.395943,73.452576,73.418213,73.451088,73.558960,73.524040,73.527283,73.593697,73.562775,73.594902,73.694901,73.689178,73.734322,73.780197,73.754349,73.809929,73.789856,73.898819,73.866638,73.834045,73.819908,73.789375,73.934486</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>72.828033,72.750816,72.721039,72.674133,72.689781,72.619278,72.550659,72.459381,72.407486,72.370018,72.383530,72.327965,72.360657,72.295120,72.306183,72.287148,72.186661,72.226280,72.103683,72.195374,72.053131,72.117805,72.087227,72.059753</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>72.987579,72.951935,72.914566,72.948784,72.944328,72.897812,72.864639,72.822929,72.790047,72.751167,72.724930,72.798126,72.748489,72.743683,72.786514,72.754318,72.685654,72.679565,72.689438,72.743568,72.635872,72.706322,72.677910,72.667786</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>73.74247741699219</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.76000213623047</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01752471923828125</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.02375910890825912</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5232371469258045</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:53</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>74.02227020263672</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>73.331970,73.351738,73.418686,73.401054,73.455940,73.425568,73.463699,73.487244,73.473602,73.493118,73.548264,73.542336,73.594833,73.621361,73.623802,73.666016,73.646255,73.674683,73.692352,73.752510,73.681984,73.746750,73.740082,73.742477</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>73.349998,73.589996,73.980003,74.160004,73.849998,74.050003,73.820000,73.870003,73.419998,73.629997,73.180000,73.040001,73.180000,73.779999,74.139999,72.669998,72.550003,73.070000,73.559998,73.550003,73.199997,73.930000,73.760002,73.760002</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.018028,0.238258,0.561317,0.758950,0.394058,0.624435,0.356301,0.382759,0.053604,0.136879,0.368264,0.502335,0.414833,0.158638,0.516197,0.996018,1.096252,0.604683,0.132354,0.202507,0.481987,0.183250,0.019920,0.017525</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.024579,0.323765,0.758742,1.023395,0.533593,0.843261,0.482661,0.518152,0.073010,0.185901,0.503230,0.687753,0.566866,0.215015,0.696247,1.370604,1.511029,0.827540,0.179927,0.275332,0.658452,0.247870,0.027007,0.023760</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5232371469258045</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>73.403824,73.395943,73.452576,73.418213,73.451088,73.558960,73.524040,73.527283,73.593697,73.562775,73.594902,73.694901,73.689178,73.734322,73.780197,73.754349,73.809929,73.789856,73.898819,73.866638,73.834045,73.819908,73.789375,73.934486</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>72.987579,72.951935,72.914566,72.948784,72.944328,72.897812,72.864639,72.822929,72.790047,72.751167,72.724930,72.798126,72.748489,72.743683,72.786514,72.754318,72.685654,72.679565,72.689438,72.743568,72.635872,72.706322,72.677910,72.667786</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:53</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>73.719849,73.748268,73.784576,73.806473,73.849609,73.855293,73.855927,73.856644,73.852417,73.839096,73.859482,73.835243,73.849892,73.866699,73.878632,73.912819,73.923706,73.964294,73.979248,73.976654,73.963654,73.973183,74.020065,74.022270</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>73.783882,73.723900,73.846321,73.827835,73.905060,73.925453,73.907242,73.899826,73.913391,73.857330,73.905869,73.973503,73.931015,73.955887,74.026047,74.009537,74.051346,74.090073,74.117523,74.037598,74.009117,74.058479,74.114449,74.127014</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>73.131775,73.043625,72.974800,72.978645,72.978439,72.919502,72.858910,72.727432,72.680283,72.598206,72.567070,72.504791,72.456718,72.427612,72.440849,72.438377,72.392441,72.415131,72.363365,72.366776,72.300705,72.302895,72.321304,72.254066</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>73.318588,73.295578,73.251770,73.269249,73.255432,73.237915,73.194588,73.118248,73.086929,73.030304,72.940880,72.972092,72.919815,72.898422,72.970741,72.970383,72.905571,72.917908,72.937561,72.945206,72.899094,72.882629,72.929886,72.903763</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>74.02227020263672</v>
+      </c>
+      <c r="G12" t="n">
+        <v>74.08000183105469</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.05773162841796875</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.07793146192089777</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5849977755967093</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:46</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>74.37374114990234</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>73.719849,73.748268,73.784576,73.806473,73.849609,73.855293,73.855927,73.856644,73.852417,73.839096,73.859482,73.835243,73.849892,73.866699,73.878632,73.912819,73.923706,73.964294,73.979248,73.976654,73.963654,73.973183,74.020065,74.022270</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>73.610001,73.419998,73.599998,73.430000,73.320000,73.709999,73.940002,73.800003,74.120003,74.309998,74.599998,74.540001,74.570000,74.519997,74.690002,74.449997,74.730003,74.419998,74.419998,74.690002,74.440002,74.430000,74.330002,74.080002</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.109848,0.328270,0.184578,0.376473,0.529609,0.145294,0.084075,0.056641,0.267586,0.470902,0.740516,0.704758,0.720108,0.653298,0.811370,0.537178,0.806297,0.455704,0.440750,0.713348,0.476348,0.456817,0.309937,0.057732</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.149230,0.447112,0.250785,0.512696,0.722326,0.197116,0.113708,0.076749,0.361017,0.633699,0.992649,0.945476,0.965680,0.876674,1.086317,0.721529,1.078947,0.612341,0.592247,0.955079,0.639909,0.613754,0.416974,0.077932</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5849977755967093</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>73.783882,73.723900,73.846321,73.827835,73.905060,73.925453,73.907242,73.899826,73.913391,73.857330,73.905869,73.973503,73.931015,73.955887,74.026047,74.009537,74.051346,74.090073,74.117523,74.037598,74.009117,74.058479,74.114449,74.127014</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>73.318588,73.295578,73.251770,73.269249,73.255432,73.237915,73.194588,73.118248,73.086929,73.030304,72.940880,72.972092,72.919815,72.898422,72.970741,72.970383,72.905571,72.917908,72.937561,72.945206,72.899094,72.882629,72.929886,72.903763</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:46</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>74.059830,74.058762,74.076721,74.081894,74.126022,74.143379,74.172081,74.219978,74.210976,74.235672,74.225464,74.241051,74.278114,74.285538,74.269920,74.300529,74.286919,74.298309,74.322632,74.332733,74.344772,74.365723,74.350624,74.373741</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>74.111382,74.110123,74.086838,74.096245,74.156235,74.181465,74.230995,74.213493,74.285957,74.211243,74.304955,74.337502,74.356575,74.340134,74.348640,74.351044,74.427048,74.439240,74.460846,74.485268,74.458893,74.462021,74.508133,74.490768</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>73.653702,73.533669,73.419991,73.374084,73.330177,73.274117,73.238907,73.217598,73.161499,73.148018,73.104080,73.103928,73.093178,73.065125,73.031998,73.006470,72.956017,72.944077,72.902138,72.895813,72.848167,72.837791,72.818909,72.792557</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>73.802109,73.728233,73.661774,73.625092,73.597122,73.577682,73.554665,73.548904,73.544846,73.512154,73.448601,73.516006,73.490219,73.467941,73.475327,73.443985,73.413826,73.373856,73.411385,73.401184,73.399696,73.370850,73.359856,73.355934</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>74.37374114990234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>72.87000274658203</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.503738403320312</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.063590430413213</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.380433775366321</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:39:55</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>73.16261291503906</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>74.059830,74.058762,74.076721,74.081894,74.126022,74.143379,74.172081,74.219978,74.210976,74.235672,74.225464,74.241051,74.278114,74.285538,74.269920,74.300529,74.286919,74.298309,74.322632,74.332733,74.344772,74.365723,74.350624,74.373741</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>73.750000,74.169998,74.029999,73.599998,73.580002,73.419998,73.480003,73.489998,73.550003,73.199997,72.949997,73.000000,73.250000,73.279999,73.019997,73.000000,72.889999,72.650002,72.769997,72.790001,72.949997,72.980003,73.010002,72.870003</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.309830,0.111236,0.046722,0.481896,0.546020,0.723381,0.692078,0.729980,0.660973,1.035675,1.275467,1.241051,1.028114,1.005539,1.249923,1.300529,1.396920,1.648307,1.552635,1.542732,1.394775,1.385720,1.340622,1.503738</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.420108,0.149975,0.063113,0.654749,0.742077,0.985264,0.941858,0.993305,0.898672,1.414857,1.748413,1.700070,1.403569,1.372188,1.711755,1.781547,1.916476,2.268833,2.133620,2.119429,1.911960,1.898766,1.836217,2.063590</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.380433775366321</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>74.111382,74.110123,74.086838,74.096245,74.156235,74.181465,74.230995,74.213493,74.285957,74.211243,74.304955,74.337502,74.356575,74.340134,74.348640,74.351044,74.427048,74.439240,74.460846,74.485268,74.458893,74.462021,74.508133,74.490768</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>73.802109,73.728233,73.661774,73.625092,73.597122,73.577682,73.554665,73.548904,73.544846,73.512154,73.448601,73.516006,73.490219,73.467941,73.475327,73.443985,73.413826,73.373856,73.411385,73.401184,73.399696,73.370850,73.359856,73.355934</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:39:55</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>72.860252,72.867294,72.912323,72.859993,72.897110,72.908913,72.911835,72.942596,72.940636,72.937775,72.956779,72.975906,73.003906,73.027954,73.033562,73.034126,73.008301,73.065887,73.059769,73.098717,73.107086,73.131516,73.131516,73.162613</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>72.937416,72.895355,72.975128,72.971397,72.938354,73.008293,73.033356,73.001724,73.073654,73.068459,73.121414,73.195343,73.192085,73.221970,73.224831,73.162903,73.313156,73.328056,73.326424,73.382439,73.357269,73.350502,73.389252,73.496780</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>72.567909,72.495026,72.460846,72.361053,72.367485,72.325600,72.265549,72.250824,72.233925,72.215576,72.211472,72.191597,72.177231,72.166702,72.160812,72.114929,72.042221,72.096718,72.016129,72.051468,71.991119,72.018570,71.978065,71.956161</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>72.658684,72.636887,72.616379,72.538460,72.527809,72.510704,72.474358,72.471680,72.484596,72.454010,72.400017,72.490814,72.420052,72.434196,72.472878,72.420509,72.367020,72.388702,72.386215,72.401535,72.383636,72.371201,72.335831,72.380379</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>73.16261291503906</v>
+      </c>
+      <c r="G14" t="n">
+        <v>73.12000274658203</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.04261016845703125</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05827429821728644</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7820860843392601</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:46</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>73.65979766845703</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>72.860252,72.867294,72.912323,72.859993,72.897110,72.908913,72.911835,72.942596,72.940636,72.937775,72.956779,72.975906,73.003906,73.027954,73.033562,73.034126,73.008301,73.065887,73.059769,73.098717,73.107086,73.131516,73.131516,73.162613</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>73.089996,72.879997,72.930000,72.900002,72.970001,72.769997,72.769997,72.830002,72.860001,72.910004,72.970001,72.730003,72.629997,71.870003,71.029999,71.199997,71.489998,71.800003,71.849998,71.879997,72.040001,72.559998,73.059998,73.120003</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.229744,0.012703,0.017677,0.040009,0.072891,0.138916,0.141838,0.112594,0.080635,0.027771,0.013222,0.245903,0.373909,1.157951,2.003563,1.834129,1.518303,1.265884,1.209771,1.218720,1.067085,0.571518,0.071518,0.042610</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.314331,0.017430,0.024239,0.054881,0.099892,0.190898,0.194913,0.154599,0.110672,0.038090,0.018120,0.338103,0.514813,1.611175,2.820728,2.576024,2.123798,1.763069,1.683745,1.695492,1.481240,0.787649,0.097890,0.058274</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7820860843392601</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>72.937416,72.895355,72.975128,72.971397,72.938354,73.008293,73.033356,73.001724,73.073654,73.068459,73.121414,73.195343,73.192085,73.221970,73.224831,73.162903,73.313156,73.328056,73.326424,73.382439,73.357269,73.350502,73.389252,73.496780</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>72.658684,72.636887,72.616379,72.538460,72.527809,72.510704,72.474358,72.471680,72.484596,72.454010,72.400017,72.490814,72.420052,72.434196,72.472878,72.420509,72.367020,72.388702,72.386215,72.401535,72.383636,72.371201,72.335831,72.380379</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:46</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>73.050003,73.124260,73.179901,73.214218,73.272148,73.313721,73.327995,73.416367,73.443642,73.448509,73.467796,73.502075,73.512100,73.522911,73.516289,73.540512,73.520020,73.552673,73.548134,73.578964,73.618034,73.603714,73.642044,73.659798</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>73.117393,73.086548,73.223167,73.329582,73.285156,73.356651,73.432014,73.490982,73.530830,73.511848,73.581108,73.707123,73.634590,73.695404,73.648071,73.635292,73.697075,73.728035,73.720474,73.761810,73.702789,73.723274,73.833046,73.877480</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>72.568611,72.528152,72.464165,72.408554,72.406891,72.331688,72.252182,72.273315,72.245743,72.163795,72.138924,72.114357,72.033768,71.998329,71.982323,71.948792,71.846306,71.893509,71.755066,71.791382,71.784798,71.761330,71.739075,71.674080</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>72.732864,72.754272,72.721062,72.702789,72.698296,72.668488,72.655304,72.674797,72.666939,72.600388,72.508987,72.602921,72.516243,72.481766,72.519112,72.488419,72.394424,72.405190,72.381111,72.406075,72.429153,72.365097,72.390465,72.385956</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>73.65979766845703</v>
+      </c>
+      <c r="G15" t="n">
+        <v>72.87999725341797</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7798004150390625</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.069978655909583</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4539850547514638</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:41:55</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>72.82270050048828</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>73.050003,73.124260,73.179901,73.214218,73.272148,73.313721,73.327995,73.416367,73.443642,73.448509,73.467796,73.502075,73.512100,73.522911,73.516289,73.540512,73.520020,73.552673,73.548134,73.578964,73.618034,73.603714,73.642044,73.659798</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>73.449997,73.529999,73.379997,73.400002,73.120003,73.309998,73.209999,72.940002,72.879997,72.900002,73.029999,72.970001,73.080002,73.250000,73.489998,73.650002,73.599998,73.910004,73.570000,73.540001,73.160004,72.930000,72.949997,72.879997</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.399994,0.405739,0.200096,0.185784,0.152145,0.003723,0.117996,0.476365,0.563645,0.548507,0.437797,0.532074,0.432098,0.272911,0.026291,0.109490,0.079978,0.357331,0.021866,0.038963,0.458030,0.673714,0.692047,0.779801</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.544580,0.551800,0.272685,0.253111,0.208076,0.005079,0.161175,0.653091,0.773387,0.752411,0.599476,0.729168,0.591267,0.372575,0.035775,0.148662,0.108666,0.483467,0.029721,0.052982,0.626067,0.923781,0.948659,1.069979</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4539850547514638</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>73.117393,73.086548,73.223167,73.329582,73.285156,73.356651,73.432014,73.490982,73.530830,73.511848,73.581108,73.707123,73.634590,73.695404,73.648071,73.635292,73.697075,73.728035,73.720474,73.761810,73.702789,73.723274,73.833046,73.877480</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>72.732864,72.754272,72.721062,72.702789,72.698296,72.668488,72.655304,72.674797,72.666939,72.600388,72.508987,72.602921,72.516243,72.481766,72.519112,72.488419,72.394424,72.405190,72.381111,72.406075,72.429153,72.365097,72.390465,72.385956</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:41:55</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>72.877480,72.874741,72.893539,72.878036,72.888100,72.852570,72.820473,72.836197,72.819427,72.826546,72.831314,72.848480,72.840729,72.862122,72.847687,72.870140,72.848770,72.854507,72.837997,72.807098,72.830116,72.822823,72.814270,72.822701</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>72.903343,72.890594,72.854820,72.943695,72.859802,72.859421,72.857559,72.873886,72.912445,72.908188,72.880844,73.002632,72.959122,72.887115,72.953163,72.921158,72.936615,72.916397,72.866501,72.943626,72.905273,72.904724,72.936966,72.991753</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>72.499153,72.392426,72.347618,72.273514,72.222771,72.090179,72.010651,71.957680,71.910393,71.852158,71.829834,71.780579,71.709618,71.699997,71.644302,71.606316,71.512390,71.509918,71.406906,71.324280,71.341141,71.290466,71.244812,71.204369</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>72.637527,72.591652,72.566910,72.513847,72.482201,72.395004,72.331146,72.320457,72.304436,72.217056,72.177917,72.210159,72.132576,72.095634,72.102493,72.073326,72.033913,71.975037,71.974716,71.899689,71.911148,71.883530,71.841415,71.805901</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>72.82270050048828</v>
+      </c>
+      <c r="G16" t="n">
+        <v>73.44999694824219</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6272964477539062</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8540455736110399</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7991613084907327</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>73.18791198730469</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>72.877480,72.874741,72.893539,72.878036,72.888100,72.852570,72.820473,72.836197,72.819427,72.826546,72.831314,72.848480,72.840729,72.862122,72.847687,72.870140,72.848770,72.854507,72.837997,72.807098,72.830116,72.822823,72.814270,72.822701</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>72.769997,72.839996,72.510002,72.430000,72.269997,72.650002,72.529999,72.360001,72.330002,73.180000,73.699997,73.540001,73.339996,73.620003,73.900002,73.949997,73.809998,73.650002,73.480003,73.489998,73.000000,73.680000,73.800003,73.449997</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.107483,0.034745,0.383537,0.448036,0.618103,0.202568,0.290474,0.476196,0.489425,0.353454,0.868683,0.691521,0.499267,0.757881,1.052315,1.079857,0.961228,0.795495,0.642006,0.682900,0.169884,0.857177,0.985733,0.627296</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.147703,0.047700,0.528943,0.618578,0.855270,0.278828,0.400488,0.658093,0.676656,0.482993,1.178674,0.940333,0.680757,1.029449,1.423971,1.460253,1.302300,1.080101,0.873716,0.929242,0.232718,1.163379,1.335682,0.854045</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7991613084907327</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>72.903343,72.890594,72.854820,72.943695,72.859802,72.859421,72.857559,72.873886,72.912445,72.908188,72.880844,73.002632,72.959122,72.887115,72.953163,72.921158,72.936615,72.916397,72.866501,72.943626,72.905273,72.904724,72.936966,72.991753</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>72.637527,72.591652,72.566910,72.513847,72.482201,72.395004,72.331146,72.320457,72.304436,72.217056,72.177917,72.210159,72.132576,72.095634,72.102493,72.073326,72.033913,71.975037,71.974716,71.899689,71.911148,71.883530,71.841415,71.805901</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>73.386787,73.390244,73.370148,73.370560,73.363281,73.344467,73.320763,73.335732,73.323082,73.335625,73.310516,73.340385,73.313469,73.340187,73.298271,73.331459,73.278244,73.255936,73.266487,73.219826,73.257645,73.232536,73.195534,73.187912</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>73.387970,73.419289,73.289215,73.360863,73.393158,73.353500,73.339317,73.417831,73.432487,73.362244,73.396225,73.348061,73.452576,73.342323,73.375893,73.358017,73.334854,73.341095,73.366646,73.261909,73.317108,73.361435,73.258537,73.291534</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>72.970436,72.784409,72.673943,72.663025,72.513008,72.463890,72.367752,72.314240,72.294067,72.269180,72.190880,72.130585,72.073189,72.182922,72.097992,72.130226,71.962738,71.944443,71.874374,71.819244,71.876640,71.818001,71.793999,71.791382</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>73.095222,73.037048,72.952072,72.920837,72.820320,72.764404,72.687759,72.707069,72.714249,72.627655,72.537315,72.566574,72.519173,72.530785,72.448723,72.481323,72.444901,72.301056,72.367302,72.287003,72.304787,72.293449,72.294464,72.275345</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>73.18791198730469</v>
+      </c>
+      <c r="G17" t="n">
+        <v>73.80999755859375</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6220855712890625</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8428202030425791</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6327984525991582</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:20:56</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>73.65591430664062</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>73.386787,73.390244,73.370148,73.370560,73.363281,73.344467,73.320763,73.335732,73.323082,73.335625,73.310516,73.340385,73.313469,73.340187,73.298271,73.331459,73.278244,73.255936,73.266487,73.219826,73.257645,73.232536,73.195534,73.187912</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>73.760002,73.680000,73.349998,73.599998,73.279999,73.220001,73.540001,73.870003,73.750000,73.559998,73.739998,73.919998,73.660004,73.709999,74.099998,74.139999,74.209999,74.070000,74.050003,73.449997,73.449997,74.059998,74.160004,73.809998</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.373215,0.289756,0.020150,0.229438,0.083282,0.124466,0.219238,0.534271,0.426918,0.224373,0.429482,0.579613,0.346535,0.369812,0.801727,0.808540,0.931755,0.814064,0.783516,0.230171,0.192352,0.827462,0.964470,0.622086</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.505986,0.393263,0.027470,0.311737,0.113649,0.169989,0.298121,0.723258,0.578872,0.305020,0.582427,0.784109,0.470452,0.501712,1.081953,1.090559,1.255565,1.099046,1.058091,0.313371,0.261881,1.117285,1.300525,0.842820</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6327984525991582</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>73.387970,73.419289,73.289215,73.360863,73.393158,73.353500,73.339317,73.417831,73.432487,73.362244,73.396225,73.348061,73.452576,73.342323,73.375893,73.358017,73.334854,73.341095,73.366646,73.261909,73.317108,73.361435,73.258537,73.291534</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>73.095222,73.037048,72.952072,72.920837,72.820320,72.764404,72.687759,72.707069,72.714249,72.627655,72.537315,72.566574,72.519173,72.530785,72.448723,72.481323,72.444901,72.301056,72.367302,72.287003,72.304787,72.293449,72.294464,72.275345</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:20:56</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>73.795387,73.815323,73.805077,73.801704,73.780167,73.771049,73.769424,73.752159,73.766510,73.755196,73.765869,73.786369,73.762077,73.781097,73.750298,73.757149,73.732323,73.716644,73.716736,73.689812,73.711205,73.689240,73.671005,73.655914</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>73.792274,73.866684,73.718430,73.809631,73.752869,73.735939,73.748276,73.779129,73.818573,73.792923,73.815277,73.822929,73.815742,73.768150,73.782486,73.776993,73.785538,73.743240,73.737900,73.724533,73.773636,73.795952,73.740349,73.677353</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>73.362534,73.194534,73.092926,73.047005,72.903755,72.832130,72.752182,72.681595,72.667297,72.614029,72.560417,72.506104,72.456146,72.508179,72.412033,72.412010,72.302940,72.273766,72.189430,72.141975,72.174652,72.115486,72.084648,72.061493</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>73.490387,73.427864,73.367844,73.313766,73.210861,73.151451,73.113182,73.087914,73.096024,73.003654,72.950134,72.970505,72.922768,72.916565,72.833801,72.837662,72.834953,72.702164,72.741165,72.677155,72.690041,72.659622,72.652252,72.608124</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>73.65591430664062</v>
+      </c>
+      <c r="G18" t="n">
+        <v>73.44999694824219</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2059173583984375</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2803503974867974</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3557160481215166</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:43</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>73.52577209472656</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>73.795387,73.815323,73.805077,73.801704,73.780167,73.771049,73.769424,73.752159,73.766510,73.755196,73.765869,73.786369,73.762077,73.781097,73.750298,73.757149,73.732323,73.716644,73.716736,73.689812,73.711205,73.689240,73.671005,73.655914</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>73.730003,74.089996,73.949997,73.910004,74.019997,73.949997,73.769997,73.699997,74.000000,73.910004,73.889999,73.889999,74.209999,74.470001,74.459999,74.410004,74.320000,74.050003,73.949997,73.970001,74.010002,73.680000,73.470001,73.449997</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.065384,0.274673,0.144920,0.108300,0.239830,0.178948,0.000573,0.052162,0.233490,0.154808,0.124130,0.103630,0.447922,0.688904,0.709701,0.652855,0.587677,0.333359,0.233261,0.280189,0.298797,0.009240,0.201004,0.205917</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.088680,0.370729,0.195970,0.146529,0.324007,0.241985,0.000776,0.070776,0.315527,0.209454,0.167993,0.140250,0.603587,0.925076,0.953131,0.877375,0.790738,0.450181,0.315431,0.378788,0.403725,0.012540,0.273586,0.280350</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3557160481215166</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>73.792274,73.866684,73.718430,73.809631,73.752869,73.735939,73.748276,73.779129,73.818573,73.792923,73.815277,73.822929,73.815742,73.768150,73.782486,73.776993,73.785538,73.743240,73.737900,73.724533,73.773636,73.795952,73.740349,73.677353</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>73.490387,73.427864,73.367844,73.313766,73.210861,73.151451,73.113182,73.087914,73.096024,73.003654,72.950134,72.970505,72.922768,72.916565,72.833801,72.837662,72.834953,72.702164,72.741165,72.677155,72.690041,72.659622,72.652252,72.608124</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:43</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>73.504196,73.518311,73.509735,73.503647,73.504250,73.496758,73.484550,73.492744,73.496956,73.502609,73.507179,73.515060,73.530975,73.549454,73.548584,73.552582,73.543236,73.551346,73.550842,73.550468,73.551201,73.546227,73.527542,73.525772</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>73.514214,73.531609,73.497231,73.529495,73.494553,73.509850,73.506676,73.513840,73.534645,73.503960,73.539757,73.596352,73.569183,73.574799,73.571419,73.569458,73.607132,73.589386,73.594322,73.599510,73.604218,73.597145,73.554993,73.577217</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>73.070572,72.967003,72.870079,72.801086,72.730202,72.687042,72.594078,72.533401,72.499107,72.460419,72.443840,72.426636,72.409241,72.409973,72.371445,72.340073,72.291817,72.279884,72.204361,72.187973,72.183983,72.129440,72.090309,72.050674</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>73.231186,73.183701,73.115349,73.066429,73.025497,72.990616,72.937134,72.903023,72.893448,72.854424,72.808350,72.838425,72.823059,72.813599,72.816353,72.792694,72.760727,72.736992,72.734253,72.714890,72.715080,72.680878,72.659714,72.608704</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>73.52577209472656</v>
+      </c>
+      <c r="G19" t="n">
+        <v>72.66000366210938</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8657684326171875</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.191533703525901</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7441330504272293</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:54</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="n">
+        <v>72.928466796875</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>73.504196,73.518311,73.509735,73.503647,73.504250,73.496758,73.484550,73.492744,73.496956,73.502609,73.507179,73.515060,73.530975,73.549454,73.548584,73.552582,73.543236,73.551346,73.550842,73.550468,73.551201,73.546227,73.527542,73.525772</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>73.800003,74.150002,73.980003,73.800003,73.910004,73.220001,73.220001,73.379997,73.070000,73.169998,73.389999,73.250000,73.370003,73.120003,72.750000,72.739998,72.790001,72.800003,72.629997,72.629997,72.589996,72.669998,72.639999,72.660004</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.295807,0.631691,0.470268,0.296356,0.405754,0.276757,0.264549,0.112747,0.426956,0.332611,0.117180,0.265060,0.160972,0.429451,0.798584,0.812584,0.753235,0.751343,0.920845,0.920471,0.961205,0.876229,0.887543,0.865768</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.400823,0.851909,0.635670,0.401566,0.548983,0.377980,0.361307,0.153648,0.584311,0.454573,0.159667,0.361857,0.219398,0.587324,1.097710,1.117108,1.034806,1.032064,1.267857,1.267342,1.324156,1.205764,1.221837,1.191534</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7441330504272293</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>73.514214,73.531609,73.497231,73.529495,73.494553,73.509850,73.506676,73.513840,73.534645,73.503960,73.539757,73.596352,73.569183,73.574799,73.571419,73.569458,73.607132,73.589386,73.594322,73.599510,73.604218,73.597145,73.554993,73.577217</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>73.231186,73.183701,73.115349,73.066429,73.025497,72.990616,72.937134,72.903023,72.893448,72.854424,72.808350,72.838425,72.823059,72.813599,72.816353,72.792694,72.760727,72.736992,72.734253,72.714890,72.715080,72.680878,72.659714,72.608704</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:54</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>72.656876,72.668243,72.651848,72.647278,72.659645,72.656387,72.636406,72.652351,72.673958,72.688126,72.715210,72.746742,72.778763,72.813240,72.820160,72.834793,72.832062,72.863304,72.852264,72.888168,72.892212,72.918076,72.923843,72.928467</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>72.697441,72.693497,72.646431,72.675171,72.680008,72.679520,72.718567,72.660995,72.746727,72.722778,72.774513,72.866234,72.886185,72.932838,72.923668,72.887680,72.992401,72.994804,72.991806,73.001564,73.021461,73.015984,73.037369,73.080093</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>72.359619,72.279823,72.202515,72.157692,72.095604,72.067245,71.999802,71.964935,71.969742,71.948273,71.967941,71.973587,71.942444,71.928146,71.924103,71.894424,71.846298,71.859238,71.765549,71.808578,71.786758,71.799194,71.776077,71.731796</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>72.474884,72.434174,72.368858,72.336624,72.313095,72.282562,72.238586,72.225052,72.258514,72.244370,72.231766,72.279198,72.244011,72.251511,72.269531,72.244705,72.208420,72.201622,72.193604,72.221291,72.221153,72.223129,72.221931,72.193878</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>72.928466796875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>73.88999938964844</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9615325927734375</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.301302748296061</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.033247206715368</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:07:54</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="n">
+        <v>73.80706787109375</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>72.656876,72.668243,72.651848,72.647278,72.659645,72.656387,72.636406,72.652351,72.673958,72.688126,72.715210,72.746742,72.778763,72.813240,72.820160,72.834793,72.832062,72.863304,72.852264,72.888168,72.892212,72.918076,72.923843,72.928467</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>72.610001,72.809998,72.779999,72.870003,73.129997,73.570000,73.480003,73.580002,73.839996,74.080002,73.669998,73.830002,73.519997,73.370003,73.339996,73.970001,73.779999,73.690002,73.690002,73.669998,73.669998,73.849998,73.889999,73.889999</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.046875,0.141755,0.128151,0.222725,0.470352,0.913613,0.843597,0.927651,1.166038,1.391876,0.954788,1.083260,0.741234,0.556763,0.519836,1.135208,0.947937,0.826698,0.837738,0.781830,0.777786,0.931922,0.966156,0.961532</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.064558,0.194691,0.176080,0.305647,0.643173,1.241828,1.148064,1.260738,1.579142,1.878882,1.296034,1.467235,1.008207,0.758842,0.708803,1.534687,1.284815,1.121860,1.136841,1.061260,1.055771,1.261913,1.307560,1.301302</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1.033247206715368</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>72.697441,72.693497,72.646431,72.675171,72.680008,72.679520,72.718567,72.660995,72.746727,72.722778,72.774513,72.866234,72.886185,72.932838,72.923668,72.887680,72.992401,72.994804,72.991806,73.001564,73.021461,73.015984,73.037369,73.080093</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>72.474884,72.434174,72.368858,72.336624,72.313095,72.282562,72.238586,72.225052,72.258514,72.244370,72.231766,72.279198,72.244011,72.251511,72.269531,72.244705,72.208420,72.201622,72.193604,72.221291,72.221153,72.223129,72.221931,72.193878</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:07:54</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>73.874695,73.884064,73.899948,73.896645,73.894318,73.892700,73.889450,73.889305,73.894669,73.886536,73.894386,73.894722,73.890442,73.881866,73.869873,73.857277,73.852356,73.837296,73.831322,73.834358,73.829903,73.816071,73.801567,73.807068</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>73.891396,73.906265,73.882477,73.891876,73.857269,73.871353,73.870598,73.889160,73.897545,73.854622,73.874176,73.886703,73.908356,73.891815,73.895851,73.865005,73.843819,73.826248,73.839394,73.804703,73.815712,73.863670,73.793144,73.803169</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>73.492813,73.387085,73.306351,73.247055,73.153976,73.112015,73.036819,73.005478,72.960144,72.920151,72.906227,72.862450,72.804092,72.755936,72.721191,72.673782,72.622108,72.584953,72.510284,72.513374,72.486023,72.461319,72.423203,72.374008</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>73.651558,73.583328,73.536682,73.499176,73.438889,73.398026,73.360893,73.339333,73.337952,73.297752,73.267761,73.256454,73.204674,73.170738,73.162674,73.123146,73.096771,73.039795,73.031006,73.021378,73.014847,72.968796,72.958534,72.938812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>73.80706787109375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>75.80999755859375</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.0029296875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.64203898166852</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.254944240446136</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:18:57</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>75.41425323486328</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>73.874695,73.884064,73.899948,73.896645,73.894318,73.892700,73.889450,73.889305,73.894669,73.886536,73.894386,73.894722,73.890442,73.881866,73.869873,73.857277,73.852356,73.837296,73.831322,73.834358,73.829903,73.816071,73.801567,73.807068</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>74.790001,74.599998,74.620003,74.669998,74.779999,74.760002,74.830002,75.029999,75.550003,75.389999,75.480003,76.430000,76.330002,76.330002,76.330002,76.080002,76.089996,76.199997,76.150002,75.830002,75.980003,75.959999,75.809998,75.809998</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.915306,0.715934,0.720055,0.773353,0.885681,0.867302,0.940552,1.140694,1.655334,1.503463,1.585617,2.535278,2.439560,2.448136,2.460129,2.222725,2.237640,2.362701,2.318680,1.995644,2.150100,2.143928,2.008431,2.002930</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.223835,0.959698,0.964962,1.035695,1.184382,1.160115,1.256918,1.520317,2.191044,1.994248,2.100712,3.317125,3.196069,3.207305,3.223017,2.921563,2.940781,3.100658,3.044884,2.631734,2.829824,2.822444,2.649295,2.642039</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2.254944240446136</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>73.891396,73.906265,73.882477,73.891876,73.857269,73.871353,73.870598,73.889160,73.897545,73.854622,73.874176,73.886703,73.908356,73.891815,73.895851,73.865005,73.843819,73.826248,73.839394,73.804703,73.815712,73.863670,73.793144,73.803169</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>73.651558,73.583328,73.536682,73.499176,73.438889,73.398026,73.360893,73.339333,73.337952,73.297752,73.267761,73.256454,73.204674,73.170738,73.162674,73.123146,73.096771,73.039795,73.031006,73.021378,73.014847,72.968796,72.958534,72.938812</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:18:57</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>75.820419,75.780228,75.785919,75.757446,75.727318,75.706909,75.692596,75.664230,75.681778,75.678253,75.674690,75.670235,75.646721,75.629799,75.641998,75.597733,75.598213,75.555649,75.498413,75.455330,75.434059,75.430519,75.426468,75.414253</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>75.804825,75.737701,75.788605,75.742195,75.688049,75.642181,75.660828,75.689514,75.622017,75.577019,75.617691,75.552170,75.597908,75.525269,75.551697,75.533203,75.486069,75.423553,75.371628,75.367065,75.333542,75.400620,75.326698,75.318031</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>75.343704,75.195663,75.078079,74.968582,74.843346,74.762589,74.667679,74.583618,74.544777,74.477158,74.440002,74.397491,74.348763,74.261734,74.210030,74.095238,74.041077,73.987617,73.847328,73.744392,73.693169,73.683952,73.645798,73.578598</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>75.556763,75.428085,75.357849,75.295303,75.194107,75.122223,75.048180,74.998070,74.983902,74.943428,74.921341,74.884186,74.837654,74.784836,74.748474,74.673218,74.636528,74.585075,74.491623,74.434372,74.385185,74.338013,74.324799,74.311455</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>75.41425323486328</v>
+      </c>
+      <c r="G22" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.085746765136719</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.419276817172181</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.30389646395552</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:16</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>76.33348846435547</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>75.820419,75.780228,75.785919,75.757446,75.727318,75.706909,75.692596,75.664230,75.681778,75.678253,75.674690,75.670235,75.646721,75.629799,75.641998,75.597733,75.598213,75.555649,75.498413,75.455330,75.434059,75.430519,75.426468,75.414253</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>75.930000,75.910004,75.940002,76.349998,76.290001,76.260002,76.389999,76.320000,76.440002,76.309998,76.529999,76.959999,77.360001,77.279999,77.120003,77.150002,77.169998,77.209999,77.290001,76.769997,76.230003,76.480003,76.830002,76.500000</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.109581,0.129776,0.154083,0.592552,0.562683,0.553093,0.697403,0.655770,0.758224,0.631745,0.855309,1.289764,1.713280,1.650200,1.478005,1.552269,1.571785,1.654350,1.791588,1.314667,0.795944,1.049484,1.403534,1.085747</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.144319,0.170960,0.202902,0.776100,0.737558,0.725273,0.912951,0.859237,0.991921,0.827866,1.117612,1.675889,2.214684,2.135352,1.916500,2.012014,2.036783,2.142663,2.318007,1.712475,1.044135,1.372234,1.826804,1.419277</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1.30389646395552</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>75.804825,75.737701,75.788605,75.742195,75.688049,75.642181,75.660828,75.689514,75.622017,75.577019,75.617691,75.552170,75.597908,75.525269,75.551697,75.533203,75.486069,75.423553,75.371628,75.367065,75.333542,75.400620,75.326698,75.318031</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>75.556763,75.428085,75.357849,75.295303,75.194107,75.122223,75.048180,74.998070,74.983902,74.943428,74.921341,74.884186,74.837654,74.784836,74.748474,74.673218,74.636528,74.585075,74.491623,74.434372,74.385185,74.338013,74.324799,74.311455</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:16</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>76.517670,76.464005,76.456139,76.455879,76.465752,76.453110,76.467422,76.466835,76.489334,76.491341,76.509056,76.499054,76.527725,76.509415,76.509781,76.470161,76.467087,76.459007,76.405090,76.358688,76.352028,76.345566,76.360077,76.333488</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>76.511322,76.384567,76.462875,76.450287,76.436714,76.348846,76.379349,76.431313,76.393517,76.355042,76.388794,76.342072,76.323471,76.383698,76.361961,76.360214,76.363785,76.260925,76.221252,76.232300,76.221725,76.257713,76.171661,76.149788</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>76.040970,75.864014,75.720886,75.599228,75.516800,75.416016,75.327148,75.247368,75.238007,75.178391,75.152512,75.080917,75.128448,75.004349,74.956749,74.892082,74.834793,74.811935,74.647408,74.553467,74.499115,74.477875,74.466492,74.386414</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>76.240410,76.096245,75.991432,75.947311,75.882523,75.805580,75.776352,75.707397,75.689392,75.669601,75.663826,75.625626,75.605843,75.568146,75.530273,75.498619,75.434944,75.426483,75.325890,75.275009,75.252945,75.177246,75.204475,75.152496</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>76.33348846435547</v>
+      </c>
+      <c r="G23" t="n">
+        <v>76.01999664306641</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3134918212890625</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.412380735506985</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4712381868699448</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>76.12698364257812</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>76.517670,76.464005,76.456139,76.455879,76.465752,76.453110,76.467422,76.466835,76.489334,76.491341,76.509056,76.499054,76.527725,76.509415,76.509781,76.470161,76.467087,76.459007,76.405090,76.358688,76.352028,76.345566,76.360077,76.333488</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>76.580002,76.489998,76.809998,76.940002,76.919998,76.889999,76.519997,76.760002,76.970001,76.589996,76.250000,76.199997,75.910004,75.629997,75.900002,75.730003,76.110001,76.360001,76.239998,76.239998,75.809998,75.809998,76.019997,76.019997</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.062332,0.025993,0.353859,0.484123,0.454246,0.436889,0.052575,0.293167,0.480667,0.098655,0.259056,0.299057,0.617721,0.879418,0.609779,0.740158,0.357086,0.099006,0.165092,0.118690,0.542030,0.535568,0.340080,0.313491</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.081394,0.033982,0.460693,0.629222,0.590544,0.568201,0.068707,0.381927,0.624486,0.128810,0.339746,0.392463,0.813755,1.162790,0.803399,0.977364,0.469171,0.129657,0.216543,0.155680,0.714985,0.706461,0.447356,0.412380</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4712381868699448</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>76.511322,76.384567,76.462875,76.450287,76.436714,76.348846,76.379349,76.431313,76.393517,76.355042,76.388794,76.342072,76.323471,76.383698,76.361961,76.360214,76.363785,76.260925,76.221252,76.232300,76.221725,76.257713,76.171661,76.149788</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>76.240410,76.096245,75.991432,75.947311,75.882523,75.805580,75.776352,75.707397,75.689392,75.669601,75.663826,75.625626,75.605843,75.568146,75.530273,75.498619,75.434944,75.426483,75.325890,75.275009,75.252945,75.177246,75.204475,75.152496</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>76.018570,75.979614,75.963699,75.944633,75.958534,75.978668,75.992348,75.976570,75.998245,76.001312,76.017441,76.011612,76.038391,76.024857,76.056213,76.051155,76.067329,76.089897,76.078056,76.088089,76.103149,76.106895,76.143051,76.126984</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>76.047501,75.936562,75.970901,75.936951,75.924019,75.948097,75.951263,75.970695,75.954430,75.927200,75.968185,75.951675,75.912872,75.980331,76.010185,75.995331,76.002083,75.972900,76.020081,76.048988,76.033409,76.072372,76.081558,76.040916</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>75.599663,75.438103,75.322769,75.242126,75.158569,75.126320,75.057999,74.962158,74.943474,74.889130,74.858887,74.852974,74.852730,74.739105,74.731972,74.694878,74.662750,74.656189,74.529091,74.489929,74.490234,74.459404,74.464096,74.405167</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>75.760086,75.646942,75.550987,75.500526,75.459747,75.435287,75.404182,75.309662,75.326065,75.296089,75.290802,75.286446,75.247330,75.207542,75.203300,75.201706,75.164764,75.164322,75.095284,75.125488,75.112320,75.071419,75.093925,75.054550</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>76.12698364257812</v>
+      </c>
+      <c r="G24" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.373016357421875</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4876030815972222</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4782454701360944</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:37</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>76.67567443847656</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>76.018570,75.979614,75.963699,75.944633,75.958534,75.978668,75.992348,75.976570,75.998245,76.001312,76.017441,76.011612,76.038391,76.024857,76.056213,76.051155,76.067329,76.089897,76.078056,76.088089,76.103149,76.106895,76.143051,76.126984</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>76.000000,76.019997,75.730003,75.739998,75.620003,75.870003,75.820000,75.889999,76.139999,75.800003,75.949997,75.139999,74.870003,74.860001,75.089996,75.199997,75.570000,75.980003,76.389999,76.349998,76.150002,76.309998,76.360001,76.500000</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.018570,0.040383,0.233696,0.204635,0.338531,0.108665,0.172348,0.086571,0.141754,0.201309,0.067444,0.871613,1.168388,1.164856,0.966217,0.851158,0.497329,0.109894,0.311943,0.261909,0.046853,0.203103,0.216950,0.373016</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.024434,0.053121,0.308591,0.270181,0.447674,0.143226,0.227312,0.114074,0.186176,0.265579,0.088801,1.159985,1.560556,1.556046,1.286745,1.131859,0.658104,0.144635,0.408356,0.343038,0.061527,0.266155,0.284114,0.487603</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4782454701360944</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>76.047501,75.936562,75.970901,75.936951,75.924019,75.948097,75.951263,75.970695,75.954430,75.927200,75.968185,75.951675,75.912872,75.980331,76.010185,75.995331,76.002083,75.972900,76.020081,76.048988,76.033409,76.072372,76.081558,76.040916</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>75.760086,75.646942,75.550987,75.500526,75.459747,75.435287,75.404182,75.309662,75.326065,75.296089,75.290802,75.286446,75.247330,75.207542,75.203300,75.201706,75.164764,75.164322,75.095284,75.125488,75.112320,75.071419,75.093925,75.054550</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:37</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>76.485497,76.480316,76.488403,76.504120,76.512405,76.529785,76.547684,76.571136,76.584572,76.568916,76.577103,76.596596,76.587059,76.579536,76.585732,76.585945,76.602531,76.619011,76.602753,76.627167,76.658859,76.659576,76.691452,76.675674</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>76.509384,76.442368,76.523071,76.456276,76.510651,76.445602,76.513794,76.573982,76.487900,76.518051,76.542885,76.464508,76.489235,76.495506,76.512726,76.532547,76.514969,76.558525,76.582405,76.517273,76.588165,76.625992,76.624344,76.555000</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>76.079498,75.961082,75.872925,75.818848,75.751022,75.709763,75.659073,75.626442,75.590721,75.514496,75.472649,75.471039,75.434418,75.338562,75.279816,75.252716,75.228394,75.246658,75.143730,75.102127,75.112221,75.076248,75.063850,74.994293</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>76.230606,76.158714,76.095459,76.076546,76.034088,75.997223,75.974670,75.945786,75.946144,75.893936,75.877739,75.892502,75.833893,75.782784,75.745789,75.754860,75.723885,75.742142,75.682350,75.721886,75.706200,75.639900,75.675797,75.619270</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>76.67567443847656</v>
+      </c>
+      <c r="G25" t="n">
+        <v>75.48000335693359</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.195671081542969</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.584089862700217</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8370368555028715</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>75.40408325195312</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>76.485497,76.480316,76.488403,76.504120,76.512405,76.529785,76.547684,76.571136,76.584572,76.568916,76.577103,76.596596,76.587059,76.579536,76.585732,76.585945,76.602531,76.619011,76.602753,76.627167,76.658859,76.659576,76.691452,76.675674</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>76.349998,76.220001,76.260002,75.970001,76.180000,76.110001,76.690002,76.709999,76.769997,76.580002,76.169998,75.400002,75.680000,75.610001,75.849998,75.820000,75.690002,75.860001,75.800003,75.800003,75.550003,75.550003,75.559998,75.480003</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.135499,0.260315,0.228401,0.534119,0.332405,0.419784,0.142318,0.138863,0.185425,0.011086,0.407105,1.196594,0.907059,0.969535,0.735734,0.765945,0.912529,0.759010,0.802750,0.827164,1.108856,1.109573,1.131454,1.195671</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.177470,0.341531,0.299503,0.703065,0.436341,0.551550,0.185576,0.181023,0.241533,0.014476,0.534469,1.586995,1.198545,1.282285,0.969985,1.010215,1.205613,1.000541,1.059037,1.091245,1.467711,1.468660,1.497425,1.584089</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8370368555028715</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>76.509384,76.442368,76.523071,76.456276,76.510651,76.445602,76.513794,76.573982,76.487900,76.518051,76.542885,76.464508,76.489235,76.495506,76.512726,76.532547,76.514969,76.558525,76.582405,76.517273,76.588165,76.625992,76.624344,76.555000</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>76.230606,76.158714,76.095459,76.076546,76.034088,75.997223,75.974670,75.945786,75.946144,75.893936,75.877739,75.892502,75.833893,75.782784,75.745789,75.754860,75.723885,75.742142,75.682350,75.721886,75.706200,75.639900,75.675797,75.619270</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>75.487778,75.484940,75.478958,75.465195,75.441223,75.424896,75.436089,75.454376,75.453102,75.443619,75.441360,75.432213,75.412209,75.392273,75.383774,75.369316,75.357132,75.363113,75.346222,75.353149,75.369247,75.400650,75.415756,75.404083</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>75.476128,75.477127,75.479149,75.429443,75.399773,75.417435,75.432472,75.433464,75.430443,75.467842,75.419342,75.415527,75.385941,75.365524,75.363884,75.323021,75.337723,75.331558,75.339767,75.338783,75.379196,75.393974,75.394844,75.396225</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>75.092285,74.981812,74.874977,74.789673,74.688492,74.612305,74.566216,74.530121,74.489227,74.445831,74.378540,74.358963,74.312454,74.212502,74.164307,74.110535,74.071930,74.049843,73.965652,73.932953,73.913498,73.913849,73.898972,73.856232</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>75.250298,75.167427,75.091919,75.040543,74.959824,74.911041,74.879364,74.849495,74.843140,74.803642,74.767502,74.761642,74.695541,74.662071,74.622467,74.589233,74.549469,74.529678,74.510521,74.512558,74.493607,74.454918,74.489288,74.437317</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>75.40408325195312</v>
+      </c>
+      <c r="G26" t="n">
+        <v>76.05000305175781</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6459197998046875</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8493356658580145</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.82943957982085</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:52</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>76.01427459716797</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>75.487778,75.484940,75.478958,75.465195,75.441223,75.424896,75.436089,75.454376,75.453102,75.443619,75.441360,75.432213,75.412209,75.392273,75.383774,75.369316,75.357132,75.363113,75.346222,75.353149,75.369247,75.400650,75.415756,75.404083</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>76.180000,76.050003,76.440002,76.449997,76.370003,76.139999,76.080002,75.680000,75.599998,76.059998,76.110001,76.389999,75.580002,75.510002,75.699997,75.940002,76.129997,76.150002,76.139999,76.190002,76.209999,76.000000,76.019997,76.050003</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.692222,0.565063,0.961044,0.984802,0.928780,0.715103,0.643913,0.225624,0.146896,0.616379,0.668641,0.957786,0.167793,0.117729,0.316223,0.570686,0.772865,0.786889,0.793777,0.836853,0.840752,0.599350,0.604241,0.645920</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.908667,0.743015,1.257253,1.288165,1.216158,0.939195,0.846363,0.298129,0.194308,0.810385,0.878519,1.253811,0.222007,0.155912,0.417732,0.751496,1.015191,1.033340,1.042524,1.098377,1.103204,0.788618,0.794844,0.849336</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.82943957982085</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>75.476128,75.477127,75.479149,75.429443,75.399773,75.417435,75.432472,75.433464,75.430443,75.467842,75.419342,75.415527,75.385941,75.365524,75.363884,75.323021,75.337723,75.331558,75.339767,75.338783,75.379196,75.393974,75.394844,75.396225</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>75.250298,75.167427,75.091919,75.040543,74.959824,74.911041,74.879364,74.849495,74.843140,74.803642,74.767502,74.761642,74.695541,74.662071,74.622467,74.589233,74.549469,74.529678,74.510521,74.512558,74.493607,74.454918,74.489288,74.437317</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:52</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>76.029221,76.011879,76.020485,76.023857,76.019577,76.037262,76.068047,76.079338,76.059608,76.049004,76.052391,76.040726,76.038208,76.011246,76.017448,76.021301,76.016060,76.025116,76.012238,76.031754,76.045319,76.032562,76.029320,76.014275</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>76.028030,75.988190,76.027092,75.991013,76.007317,76.024307,76.025803,76.015938,76.034332,76.021698,76.017685,76.024208,75.967239,75.990334,75.951958,75.983765,75.974350,75.952133,75.979660,75.969315,75.976494,75.981171,75.977592,75.966705</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>75.655945,75.552048,75.463417,75.404144,75.330170,75.275497,75.267998,75.228683,75.159981,75.111671,75.080223,75.060623,75.029152,74.946800,74.936394,74.916138,74.868958,74.848701,74.763153,74.745613,74.722443,74.673050,74.640388,74.589630</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>75.791237,75.719833,75.657990,75.624245,75.552841,75.546036,75.556877,75.517426,75.484909,75.429764,75.411758,75.422531,75.394455,75.335670,75.343765,75.341698,75.289299,75.268013,75.247116,75.268272,75.236893,75.171326,75.173019,75.119644</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>76.01427459716797</v>
+      </c>
+      <c r="G27" t="n">
+        <v>75.34999847412109</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.664276123046875</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.881587440608934</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8954884431599438</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:51</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="n">
+        <v>75.32756805419922</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>76.029221,76.011879,76.020485,76.023857,76.019577,76.037262,76.068047,76.079338,76.059608,76.049004,76.052391,76.040726,76.038208,76.011246,76.017448,76.021301,76.016060,76.025116,76.012238,76.031754,76.045319,76.032562,76.029320,76.014275</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>75.690002,75.769997,75.839996,75.470001,75.510002,75.790001,75.400002,75.320000,75.440002,75.379997,75.269997,75.190002,75.570000,75.400002,75.209999,74.889999,74.919998,75.070000,75.120003,75.120003,75.269997,75.269997,75.349998,75.349998</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.339219,0.241882,0.180489,0.553856,0.509575,0.247261,0.668045,0.759338,0.619606,0.669007,0.782394,0.850724,0.468208,0.611244,0.807449,1.131302,1.096062,0.955116,0.892235,0.911751,0.775322,0.762565,0.679322,0.664277</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.448168,0.319232,0.237986,0.733875,0.674844,0.326245,0.886002,1.008150,0.821322,0.887512,1.039451,1.131432,0.619569,0.810669,1.073593,1.510618,1.462976,1.272301,1.187747,1.213726,1.030055,1.013107,0.901555,0.881588</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8954884431599438</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>76.028030,75.988190,76.027092,75.991013,76.007317,76.024307,76.025803,76.015938,76.034332,76.021698,76.017685,76.024208,75.967239,75.990334,75.951958,75.983765,75.974350,75.952133,75.979660,75.969315,75.976494,75.981171,75.977592,75.966705</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>75.791237,75.719833,75.657990,75.624245,75.552841,75.546036,75.556877,75.517426,75.484909,75.429764,75.411758,75.422531,75.394455,75.335670,75.343765,75.341698,75.289299,75.268013,75.247116,75.268272,75.236893,75.171326,75.173019,75.119644</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:51</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>75.349541,75.327171,75.313904,75.331367,75.306343,75.324020,75.328995,75.326157,75.318451,75.314262,75.314987,75.339287,75.322922,75.310577,75.296478,75.298775,75.277908,75.282761,75.275360,75.287079,75.319832,75.316109,75.312180,75.327568</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>75.374817,75.337112,75.300140,75.297920,75.311707,75.352638,75.324570,75.296066,75.371193,75.281799,75.312019,75.351822,75.312454,75.334412,75.325470,75.269089,75.233200,75.248001,75.309669,75.248024,75.253143,75.292877,75.310051,75.301331</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>74.983398,74.878777,74.778908,74.736076,74.631660,74.580986,74.572556,74.516571,74.469757,74.405937,74.375092,74.386681,74.321182,74.256119,74.220261,74.194908,74.128136,74.101730,74.011238,74.003357,74.015312,73.978394,73.945053,73.928146</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>75.131912,75.054024,74.976013,74.953133,74.867653,74.866982,74.849625,74.809082,74.782013,74.730064,74.699379,74.737236,74.687759,74.642921,74.627548,74.611557,74.549217,74.518860,74.507324,74.518814,74.511765,74.477745,74.473671,74.457939</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>75.32756805419922</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75.37000274658203</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0424346923828125</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.05630183207700212</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1844306434316235</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:53</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="n">
+        <v>75.34095001220703</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>75.349541,75.327171,75.313904,75.331367,75.306343,75.324020,75.328995,75.326157,75.318451,75.314262,75.314987,75.339287,75.322922,75.310577,75.296478,75.298775,75.277908,75.282761,75.275360,75.287079,75.319832,75.316109,75.312180,75.327568</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>75.589996,75.349998,75.459999,75.279999,75.360001,75.169998,74.989998,75.160004,75.220001,75.180000,75.349998,75.480003,75.370003,75.449997,75.410004,75.580002,75.480003,75.480003,75.440002,75.550003,75.510002,75.290001,75.400002,75.370003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.240455,0.022827,0.146095,0.051368,0.053658,0.154022,0.338997,0.166153,0.098450,0.134262,0.035011,0.140716,0.047081,0.139420,0.113526,0.281227,0.202095,0.197242,0.164642,0.262924,0.190170,0.026108,0.087822,0.042435</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.318105,0.030295,0.193606,0.068236,0.071202,0.204898,0.452056,0.221066,0.130882,0.178587,0.046465,0.186429,0.062466,0.184785,0.150545,0.372092,0.267747,0.261317,0.218243,0.348013,0.251848,0.034677,0.116474,0.056302</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1844306434316235</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>75.374817,75.337112,75.300140,75.297920,75.311707,75.352638,75.324570,75.296066,75.371193,75.281799,75.312019,75.351822,75.312454,75.334412,75.325470,75.269089,75.233200,75.248001,75.309669,75.248024,75.253143,75.292877,75.310051,75.301331</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>75.131912,75.054024,74.976013,74.953133,74.867653,74.866982,74.849625,74.809082,74.782013,74.730064,74.699379,74.737236,74.687759,74.642921,74.627548,74.611557,74.549217,74.518860,74.507324,74.518814,74.511765,74.477745,74.473671,74.457939</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:53</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>75.379738,75.383675,75.381912,75.398560,75.387711,75.389420,75.376190,75.377647,75.372551,75.372742,75.362579,75.376015,75.378326,75.369827,75.371956,75.379204,75.364319,75.359596,75.345413,75.348236,75.361519,75.337601,75.326317,75.340950</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>75.420143,75.381310,75.392303,75.382294,75.398148,75.389450,75.373985,75.366257,75.395462,75.306419,75.348518,75.349327,75.344490,75.371155,75.382278,75.332375,75.340866,75.318405,75.334106,75.289902,75.314346,75.293076,75.292953,75.307938</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>75.041611,74.981628,74.907555,74.894028,74.829849,74.783600,74.754684,74.724457,74.672379,74.618858,74.584457,74.577271,74.507683,74.457474,74.437553,74.412086,74.358665,74.332748,74.238693,74.236557,74.202530,74.144676,74.119385,74.085358</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>75.184547,75.151489,75.091499,75.094269,75.040100,75.032753,75.005318,74.984344,74.952820,74.921089,74.879265,74.891449,74.852783,74.809006,74.823753,74.812866,74.754059,74.754227,74.709167,74.711922,74.680756,74.629883,74.618011,74.608185</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>75.34095001220703</v>
+      </c>
+      <c r="G29" t="n">
+        <v>75.12000274658203</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.220947265625</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2941257422079276</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3657149543557806</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>75.12012481689453</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>75.379738,75.383675,75.381912,75.398560,75.387711,75.389420,75.376190,75.377647,75.372551,75.372742,75.362579,75.376015,75.378326,75.369827,75.371956,75.379204,75.364319,75.359596,75.345413,75.348236,75.361519,75.337601,75.326317,75.340950</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>75.489998,75.510002,75.370003,75.290001,75.300003,75.389999,75.389999,75.230003,75.180000,75.209999,75.150002,75.230003,75.320000,75.489998,75.480003,75.209999,75.110001,75.160004,74.949997,74.269997,74.290001,74.550003,74.550003,75.120003</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.110260,0.126327,0.011909,0.108559,0.087708,0.000579,0.013809,0.147644,0.192551,0.162743,0.212577,0.146012,0.058326,0.120171,0.108047,0.169205,0.254318,0.199592,0.395416,1.078239,1.071518,0.787598,0.776314,0.220947</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.146059,0.167299,0.015801,0.144188,0.116478,0.000769,0.018317,0.196256,0.256120,0.216385,0.282871,0.194087,0.077438,0.159188,0.143147,0.224977,0.338595,0.265557,0.527573,1.451783,1.442345,1.056469,1.041333,0.294126</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3657149543557806</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>75.420143,75.381310,75.392303,75.382294,75.398148,75.389450,75.373985,75.366257,75.395462,75.306419,75.348518,75.349327,75.344490,75.371155,75.382278,75.332375,75.340866,75.318405,75.334106,75.289902,75.314346,75.293076,75.292953,75.307938</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>75.184547,75.151489,75.091499,75.094269,75.040100,75.032753,75.005318,74.984344,74.952820,74.921089,74.879265,74.891449,74.852783,74.809006,74.823753,74.812866,74.754059,74.754227,74.709167,74.711922,74.680756,74.629883,74.618011,74.608185</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>75.167267,75.172455,75.166328,75.167717,75.136795,75.149529,75.139954,75.141602,75.130264,75.117874,75.116982,75.125092,75.146675,75.152527,75.153946,75.171188,75.137634,75.138885,75.117188,75.122368,75.122879,75.087379,75.102150,75.120125</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>75.204445,75.160759,75.159233,75.166794,75.129265,75.144775,75.147751,75.109116,75.161377,75.052376,75.115723,75.132828,75.112190,75.162415,75.149979,75.128494,75.138817,75.159744,75.131508,75.113991,75.101936,75.075356,75.121170,75.143074</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>74.701729,74.641281,74.560959,74.524429,74.425980,74.398575,74.373657,74.365005,74.312149,74.265610,74.247688,74.257523,74.246292,74.198586,74.189781,74.170609,74.094444,74.078499,73.987991,74.002769,73.972244,73.908401,73.915215,73.903702</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>74.891441,74.857361,74.793518,74.768661,74.695267,74.691826,74.673561,74.634216,74.619263,74.583702,74.563324,74.585762,74.589600,74.560455,74.573273,74.570541,74.492508,74.490700,74.449265,74.469124,74.446243,74.374893,74.403198,74.399651</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>75.12012481689453</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75.73999786376953</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.619873046875</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8184223189310627</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7350683538520766</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:44</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>75.687744140625</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>75.167267,75.172455,75.166328,75.167717,75.136795,75.149529,75.139954,75.141602,75.130264,75.117874,75.116982,75.125092,75.146675,75.152527,75.153946,75.171188,75.137634,75.138885,75.117188,75.122368,75.122879,75.087379,75.102150,75.120125</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>75.400002,75.430000,75.489998,75.339996,75.769997,75.709999,75.160004,75.269997,75.690002,75.620003,75.360001,75.550003,75.900002,76.029999,75.949997,75.860001,75.839996,75.739998,75.930000,75.980003,75.980003,75.970001,75.970001,75.739998</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.232735,0.257545,0.323670,0.172279,0.633202,0.560470,0.020050,0.128395,0.559738,0.502129,0.243019,0.424911,0.753327,0.877472,0.796051,0.688813,0.702362,0.601113,0.812812,0.857635,0.857124,0.882622,0.867851,0.619873</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.308666,0.341436,0.428759,0.228669,0.835689,0.740285,0.026676,0.170579,0.739514,0.664016,0.322477,0.562424,0.992525,1.154113,1.048125,0.908005,0.926111,0.793653,1.070476,1.128765,1.128092,1.161804,1.142360,0.818422</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7350683538520766</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>75.204445,75.160759,75.159233,75.166794,75.129265,75.144775,75.147751,75.109116,75.161377,75.052376,75.115723,75.132828,75.112190,75.162415,75.149979,75.128494,75.138817,75.159744,75.131508,75.113991,75.101936,75.075356,75.121170,75.143074</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>74.891441,74.857361,74.793518,74.768661,74.695267,74.691826,74.673561,74.634216,74.619263,74.583702,74.563324,74.585762,74.589600,74.560455,74.573273,74.570541,74.492508,74.490700,74.449265,74.469124,74.446243,74.374893,74.403198,74.399651</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:44</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>75.733536,75.739861,75.727783,75.744202,75.756592,75.773636,75.769394,75.787819,75.765457,75.750481,75.731300,75.726776,75.719841,75.734161,75.737915,75.745499,75.742966,75.739914,75.765259,75.749878,75.743835,75.714737,75.697159,75.687744</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>75.726837,75.758362,75.698792,75.711563,75.725220,75.739960,75.740616,75.745628,75.734390,75.682190,75.711334,75.670349,75.648041,75.661331,75.686958,75.704613,75.695221,75.687340,75.738350,75.693207,75.680191,75.697960,75.657021,75.628296</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>75.409821,75.345001,75.258957,75.228645,75.180145,75.135513,75.097893,75.092117,75.012146,74.969208,74.916626,74.905655,74.868927,74.845276,74.832062,74.799141,74.762856,74.745819,74.699951,74.645187,74.623825,74.591942,74.563148,74.535896</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>75.542877,75.490860,75.430893,75.423630,75.402069,75.379044,75.354614,75.341270,75.311752,75.274994,75.225403,75.222290,75.207954,75.208572,75.207680,75.202057,75.155930,75.148903,75.149841,75.126099,75.093124,75.027847,75.029846,75.002060</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>75.687744140625</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76.69999694824219</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.012252807617188</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.319755994645299</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.961169367490026</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:28</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>76.71778106689453</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>75.733536,75.739861,75.727783,75.744202,75.756592,75.773636,75.769394,75.787819,75.765457,75.750481,75.731300,75.726776,75.719841,75.734161,75.737915,75.745499,75.742966,75.739914,75.765259,75.749878,75.743835,75.714737,75.697159,75.687744</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>75.209999,75.430000,75.760002,75.660004,75.930000,76.019997,76.089996,75.879997,75.769997,76.250000,76.180000,76.139999,76.730003,77.139999,77.029999,76.849998,77.220001,77.129997,76.820000,76.940002,76.889999,77.019997,76.870003,76.699997</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.523537,0.309861,0.032219,0.084198,0.173408,0.246361,0.320602,0.092178,0.004540,0.499519,0.448700,0.413223,1.010162,1.405838,1.292084,1.104499,1.477035,1.390083,1.054741,1.190124,1.146164,1.305260,1.172844,1.012253</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.696100,0.410792,0.042528,0.111285,0.228379,0.324073,0.421346,0.121479,0.005991,0.655107,0.589000,0.542715,1.316515,1.822451,1.677377,1.437215,1.912762,1.802260,1.373003,1.546821,1.490655,1.694702,1.525750,1.319756</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.961169367490026</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>75.726837,75.758362,75.698792,75.711563,75.725220,75.739960,75.740616,75.745628,75.734390,75.682190,75.711334,75.670349,75.648041,75.661331,75.686958,75.704613,75.695221,75.687340,75.738350,75.693207,75.680191,75.697960,75.657021,75.628296</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>75.542877,75.490860,75.430893,75.423630,75.402069,75.379044,75.354614,75.341270,75.311752,75.274994,75.225403,75.222290,75.207954,75.208572,75.207680,75.202057,75.155930,75.148903,75.149841,75.126099,75.093124,75.027847,75.029846,75.002060</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:28</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>76.732147,76.726067,76.740547,76.770493,76.768890,76.794258,76.804375,76.805252,76.779274,76.772339,76.783119,76.793144,76.796188,76.789948,76.790970,76.791313,76.805603,76.780777,76.788948,76.760292,76.735840,76.719749,76.706345,76.717781</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>76.725494,76.687263,76.737259,76.735229,76.718323,76.751801,76.740746,76.783508,76.706398,76.732742,76.755524,76.704659,76.675934,76.700844,76.678154,76.738159,76.704491,76.632126,76.704834,76.659462,76.633598,76.688652,76.589401,76.604736</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>76.310501,76.193108,76.113731,76.072815,76.015732,75.965424,75.916931,75.878510,75.823357,75.787254,75.750977,75.722710,75.709534,75.635712,75.621033,75.584358,75.578758,75.551407,75.495384,75.412064,75.366867,75.348175,75.314140,75.296738</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>76.477150,76.390327,76.346626,76.344017,76.305542,76.269386,76.254791,76.214012,76.176064,76.153099,76.129135,76.126007,76.115044,76.069077,76.065689,76.064888,76.041367,76.024666,76.007355,75.969368,75.915115,75.865417,75.862625,75.853981</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>76.71778106689453</v>
+      </c>
+      <c r="G32" t="n">
+        <v>84.94000244140625</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.222221374511719</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9.680034304429899</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.29647101900603</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="n">
+        <v>83.25724792480469</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>76.732147,76.726067,76.740547,76.770493,76.768890,76.794258,76.804375,76.805252,76.779274,76.772339,76.783119,76.793144,76.796188,76.789948,76.790970,76.791313,76.805603,76.780777,76.788948,76.760292,76.735840,76.719749,76.706345,76.717781</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>76.750000,76.930000,76.809998,76.750000,77.010002,76.889999,77.330002,77.250000,77.309998,77.480003,78.349998,78.339996,80.800003,81.790001,81.580002,81.610001,82.279999,82.330002,83.730003,86.589996,85.730003,84.949997,84.949997,84.940002</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.017853,0.203933,0.069451,0.020493,0.241112,0.095741,0.525627,0.444748,0.530724,0.707664,1.566879,1.546852,4.003815,5.000053,4.789032,4.818688,5.474396,5.549225,6.941055,9.829704,8.994163,8.230248,8.243652,8.222221</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.023261,0.265089,0.090419,0.026701,0.313092,0.124517,0.679719,0.575726,0.686488,0.913351,1.999846,1.974537,4.955216,6.113281,5.870350,5.904531,6.653374,6.740222,8.289807,11.352009,10.491267,9.688344,9.704123,9.680034</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>4.29647101900603</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>76.725494,76.687263,76.737259,76.735229,76.718323,76.751801,76.740746,76.783508,76.706398,76.732742,76.755524,76.704659,76.675934,76.700844,76.678154,76.738159,76.704491,76.632126,76.704834,76.659462,76.633598,76.688652,76.589401,76.604736</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>76.477150,76.390327,76.346626,76.344017,76.305542,76.269386,76.254791,76.214012,76.176064,76.153099,76.129135,76.126007,76.115044,76.069077,76.065689,76.064888,76.041367,76.024666,76.007355,75.969368,75.915115,75.865417,75.862625,75.853981</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>84.922073,84.774635,84.649879,84.571198,84.433052,84.435364,84.392273,84.273033,84.195816,84.027176,83.943558,83.856903,83.689613,83.731438,83.756226,83.606491,83.578369,83.495224,83.504478,83.426910,83.378922,83.342468,83.279633,83.257248</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>84.704468,84.435364,84.581940,84.264000,84.042343,84.009018,83.801285,83.878983,83.559769,83.597412,83.451843,83.166260,83.139694,83.188095,83.125092,83.217743,82.998505,82.925156,82.960434,82.829597,82.764870,82.933228,82.669693,82.621536</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>83.405563,82.939972,82.512077,82.103249,81.709229,81.435814,81.073517,80.750114,80.658951,80.346130,80.109131,79.845016,79.895920,79.652283,79.550552,79.380829,79.336281,79.175011,79.141090,78.886749,78.924469,78.779648,78.647217,78.690506</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>83.975601,83.638870,83.300247,83.116302,82.750023,82.535118,82.356781,82.054359,81.993599,81.694351,81.506989,81.366615,81.145416,81.080719,80.986069,80.880493,80.865723,80.699203,80.717163,80.625908,80.544312,80.391556,80.284782,80.282364</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>83.25724792480469</v>
+      </c>
+      <c r="G33" t="n">
+        <v>89.19999694824219</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.9427490234375</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.662274917885645</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.368865145044865</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="n">
+        <v>89.04524230957031</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>84.922073,84.774635,84.649879,84.571198,84.433052,84.435364,84.392273,84.273033,84.195816,84.027176,83.943558,83.856903,83.689613,83.731438,83.756226,83.606491,83.578369,83.495224,83.504478,83.426910,83.378922,83.342468,83.279633,83.257248</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>84.739998,84.419998,84.779999,84.900002,85.849998,86.120003,87.430000,87.279999,87.400002,87.190002,87.000000,86.500000,86.540001,87.320000,87.709999,87.480003,86.900002,87.239998,87.559998,87.480003,87.209999,87.639999,88.230003,89.199997</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.182075,0.354637,0.130120,0.328804,1.416946,1.684639,3.037727,3.006966,3.204186,3.162826,3.056442,2.643097,2.850388,3.588562,3.953773,3.873512,3.321633,3.744774,4.055520,4.053093,3.831077,4.297531,4.950370,5.942749</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.214863,0.420086,0.153479,0.387283,1.650491,1.956153,3.474468,3.445195,3.666116,3.627510,3.513152,3.055603,3.293723,4.109668,4.507779,4.427883,3.822362,4.292497,4.631704,4.633166,4.392933,4.903619,5.610756,6.662275</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3.368865145044865</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>84.704468,84.435364,84.581940,84.264000,84.042343,84.009018,83.801285,83.878983,83.559769,83.597412,83.451843,83.166260,83.139694,83.188095,83.125092,83.217743,82.998505,82.925156,82.960434,82.829597,82.764870,82.933228,82.669693,82.621536</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>83.975601,83.638870,83.300247,83.116302,82.750023,82.535118,82.356781,82.054359,81.993599,81.694351,81.506989,81.366615,81.145416,81.080719,80.986069,80.880493,80.865723,80.699203,80.717163,80.625908,80.544312,80.391556,80.284782,80.282364</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>89.192657,89.115158,89.238358,89.380402,89.306709,89.371552,89.340263,89.202980,89.221207,89.199402,89.160538,89.191879,89.084427,89.047592,89.168274,89.135590,89.211227,89.171616,89.102386,89.007950,89.024788,89.013260,89.074081,89.045242</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>89.049393,89.018860,89.155289,89.295959,89.238167,89.160583,88.831223,88.967781,88.864304,88.852875,88.714951,88.440491,88.557915,88.622650,88.496239,88.572113,88.581291,88.324562,88.532455,88.246742,88.399689,88.400894,88.012070,88.239365</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>88.174797,87.961151,87.890175,87.773521,87.562698,87.499100,87.053375,86.736687,86.859116,86.680740,86.464005,86.151207,86.088745,85.786263,85.688354,85.594635,85.393112,85.172012,84.788376,84.327751,84.270203,84.016724,83.916100,83.951286</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>88.549866,88.421585,88.381134,88.500778,88.258575,88.154770,88.100830,87.823288,87.888817,87.779099,87.650940,87.552856,87.339684,87.158646,87.142578,87.138992,87.114372,86.903526,86.741409,86.439728,86.349152,86.186958,86.110359,86.119186</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>89.04524230957031</v>
+      </c>
+      <c r="G34" t="n">
+        <v>94.01999664306641</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.974754333496094</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.291166253049385</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.571916321454609</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:51</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>93.63442230224609</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>89.192657,89.115158,89.238358,89.380402,89.306709,89.371552,89.340263,89.202980,89.221207,89.199402,89.160538,89.191879,89.084427,89.047592,89.168274,89.135590,89.211227,89.171616,89.102386,89.007950,89.024788,89.013260,89.074081,89.045242</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>89.220001,89.070000,89.419998,90.389999,90.190002,90.379997,93.230003,91.660004,91.440002,90.260002,90.849998,91.070000,91.889999,91.320000,91.599998,91.760002,91.529999,90.940002,91.849998,93.570000,93.570000,93.879997,93.879997,94.019997</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.027344,0.045158,0.181640,1.009597,0.883293,1.008445,3.889740,2.457024,2.218795,1.060600,1.689460,1.878121,2.805572,2.272408,2.431724,2.624412,2.318772,1.768386,2.747612,4.562050,4.545212,4.866737,4.805916,4.974755</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.030648,0.050700,0.203131,1.116935,0.979370,1.115784,4.172198,2.680584,2.426504,1.175050,1.859615,2.062283,3.053186,2.488401,2.654721,2.860083,2.533346,1.944564,2.991413,4.875547,4.857552,5.183998,5.119212,5.291167</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2.571916321454609</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>89.049393,89.018860,89.155289,89.295959,89.238167,89.160583,88.831223,88.967781,88.864304,88.852875,88.714951,88.440491,88.557915,88.622650,88.496239,88.572113,88.581291,88.324562,88.532455,88.246742,88.399689,88.400894,88.012070,88.239365</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>88.549866,88.421585,88.381134,88.500778,88.258575,88.154770,88.100830,87.823288,87.888817,87.779099,87.650940,87.552856,87.339684,87.158646,87.142578,87.138992,87.114372,86.903526,86.741409,86.439728,86.349152,86.186958,86.110359,86.119186</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:51</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>94.059036,93.995636,94.065628,94.226593,94.000259,94.021652,94.047096,93.993584,94.147415,93.970551,93.977386,93.898315,93.812706,93.720688,93.861519,93.782982,93.897507,93.835358,93.734680,93.624969,93.550911,93.551849,93.603752,93.634422</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>93.974449,93.732315,94.007065,93.946556,93.605911,93.881447,93.245773,93.625740,93.430435,93.447159,93.173820,93.070557,92.877235,93.026016,92.898857,92.988998,92.711372,92.461281,92.767776,92.699890,92.725586,92.760635,91.918198,92.374954</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>93.138100,92.771927,92.429306,92.264664,91.716888,91.641602,91.210022,90.811615,91.031418,90.663239,90.435287,89.963966,89.921280,89.468918,89.292984,89.052216,88.873840,88.618088,88.094643,87.503540,87.389420,87.202019,87.118469,87.176224</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>93.499557,93.304962,92.986244,93.164154,92.662292,92.607025,92.446419,92.250626,92.399216,92.114960,92.032654,91.821732,91.538971,91.248001,91.115868,91.019432,91.009048,90.772827,90.490051,90.200546,89.976044,89.842834,89.931564,89.917847</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>93.63442230224609</v>
+      </c>
+      <c r="G35" t="n">
+        <v>96.06999969482422</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.435577392578125</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.535211200494406</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.111369761502275</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:44</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>95.24923706054688</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>94.059036,93.995636,94.065628,94.226593,94.000259,94.021652,94.047096,93.993584,94.147415,93.970551,93.977386,93.898315,93.812706,93.720688,93.861519,93.782982,93.897507,93.835358,93.734680,93.624969,93.550911,93.551849,93.603752,93.634422</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>95.629997,96.760002,99.099998,94.199997,94.269997,94.430000,94.070000,93.879997,92.860001,93.269997,93.820000,94.110001,93.209999,93.070000,94.290001,94.250000,94.449997,94.480003,94.430000,92.820000,93.790001,96.330002,96.330002,96.070000</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.570961,2.764366,5.034370,0.026596,0.269738,0.408348,0.022904,0.113587,1.287414,0.700554,0.157386,0.211686,0.602707,0.650688,0.428482,0.467018,0.552490,0.644645,0.695320,0.804969,0.239090,2.778153,2.726250,2.435578</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1.642749,2.856931,5.080091,0.028234,0.286133,0.432435,0.024348,0.120991,1.386404,0.751104,0.167753,0.224934,0.646612,0.699139,0.454430,0.495510,0.584955,0.682309,0.736334,0.867237,0.254920,2.883995,2.830115,2.535212</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1.111369761502275</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>93.974449,93.732315,94.007065,93.946556,93.605911,93.881447,93.245773,93.625740,93.430435,93.447159,93.173820,93.070557,92.877235,93.026016,92.898857,92.988998,92.711372,92.461281,92.767776,92.699890,92.725586,92.760635,91.918198,92.374954</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>93.499557,93.304962,92.986244,93.164154,92.662292,92.607025,92.446419,92.250626,92.399216,92.114960,92.032654,91.821732,91.538971,91.248001,91.115868,91.019432,91.009048,90.772827,90.490051,90.200546,89.976044,89.842834,89.931564,89.917847</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:44</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>95.702827,95.632759,95.649132,95.768341,95.668594,95.808388,95.750549,95.649811,95.713333,95.464203,95.438858,95.353439,95.289108,95.197403,95.347275,95.371208,95.346672,95.389175,95.262886,95.135254,95.150414,95.200668,95.263123,95.249237</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>95.631058,95.260986,95.681580,95.838165,95.536392,95.550331,95.140213,95.501785,95.373749,95.187340,95.023834,94.632401,94.527664,94.848694,94.664192,95.179459,94.675644,94.718475,94.701469,94.866074,94.913177,94.955292,94.621765,94.623184</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>94.435425,94.065506,93.669930,93.588577,93.117020,93.044373,92.855103,92.526993,92.487694,92.130157,91.742493,91.504654,91.466110,91.040863,90.874878,91.036903,90.689133,90.720749,90.283157,89.769135,89.816803,89.655830,89.683380,89.782654</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>94.928787,94.664780,94.378540,94.418335,94.044678,94.053299,94.002518,93.603264,93.772202,93.313385,93.143326,93.074921,92.811470,92.518494,92.462296,92.591248,92.452339,92.346527,92.166496,92.013298,91.895050,91.790436,91.923683,91.825912</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>95.24923706054688</v>
+      </c>
+      <c r="G36" t="n">
+        <v>94.16000366210938</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.0892333984375</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.15678988538083</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.267324681047306</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="n">
+        <v>93.34425354003906</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>95.702827,95.632759,95.649132,95.768341,95.668594,95.808388,95.750549,95.649811,95.713333,95.464203,95.438858,95.353439,95.289108,95.197403,95.347275,95.371208,95.346672,95.389175,95.262886,95.135254,95.150414,95.200668,95.263123,95.249237</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>94.879997,93.699997,92.610001,92.309998,92.230003,92.430000,93.180000,93.309998,93.620003,94.599998,94.570000,95.370003,95.040001,95.330002,95.379997,95.099998,95.279999,95.050003,95.050003,95.349998,95.599998,95.400002,95.540001,94.160004</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.822830,1.932762,3.039131,3.458343,3.438591,3.378388,2.570549,2.339813,2.093330,0.864205,0.868858,0.016564,0.249107,0.132599,0.032722,0.271210,0.066673,0.339172,0.212883,0.214744,0.449584,0.199334,0.276878,1.089233</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.867232,2.062713,3.281645,3.746445,3.728278,3.655077,2.758691,2.507570,2.235986,0.913535,0.918746,0.017368,0.262108,0.139095,0.034307,0.285184,0.069976,0.356835,0.223969,0.225217,0.470277,0.208945,0.289803,1.156790</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1.267324681047306</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>95.631058,95.260986,95.681580,95.838165,95.536392,95.550331,95.140213,95.501785,95.373749,95.187340,95.023834,94.632401,94.527664,94.848694,94.664192,95.179459,94.675644,94.718475,94.701469,94.866074,94.913177,94.955292,94.621765,94.623184</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>94.928787,94.664780,94.378540,94.418335,94.044678,94.053299,94.002518,93.603264,93.772202,93.313385,93.143326,93.074921,92.811470,92.518494,92.462296,92.591248,92.452339,92.346527,92.166496,92.013298,91.895050,91.790436,91.923683,91.825912</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>94.187210,94.023773,94.025612,94.135056,94.000793,94.056244,94.045273,93.929962,94.090790,93.958694,93.992577,93.977921,93.946388,93.796677,93.896927,93.801254,93.793823,93.747452,93.688683,93.609161,93.627243,93.490173,93.395142,93.344254</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>94.163284,94.000076,94.074532,94.238235,94.130081,94.048019,93.573677,93.860107,93.905708,93.797775,93.862640,93.555466,93.514832,93.686073,93.529251,93.603584,93.305077,93.307037,93.362488,93.261482,93.372383,93.230400,93.124649,92.942093</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>92.876724,92.552444,92.352974,92.426582,92.070847,91.959503,91.936287,91.722504,91.669342,91.464256,91.390854,91.237175,91.076393,90.813362,90.685211,90.714088,90.411057,90.399315,90.061287,89.825981,89.784233,89.538254,89.385872,89.344116</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>93.437912,93.127930,92.958939,93.065422,92.769691,92.797989,92.745003,92.485184,92.659584,92.433167,92.361786,92.368668,92.165474,91.876755,91.941833,91.852982,91.727951,91.645432,91.452698,91.419678,91.278961,91.051872,90.987717,90.952545</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>93.34425354003906</v>
+      </c>
+      <c r="G37" t="n">
+        <v>101.4599990844727</v>
+      </c>
+      <c r="H37" t="n">
+        <v>8.115745544433594</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.998960790130363</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.334282034131808</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:45</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="n">
+        <v>97.99116516113281</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>94.187210,94.023773,94.025612,94.135056,94.000793,94.056244,94.045273,93.929962,94.090790,93.958694,93.992577,93.977921,93.946388,93.796677,93.896927,93.801254,93.793823,93.747452,93.688683,93.609161,93.627243,93.490173,93.395142,93.344254</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>94.589996,93.660004,94.220001,94.269997,94.540001,94.050003,93.919998,94.650002,94.680000,95.820000,96.260002,95.000000,96.080002,96.430000,96.050003,95.370003,95.910004,96.519997,96.500000,96.629997,96.629997,101.750000,101.750000,101.459999</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.402786,0.363769,0.194389,0.134941,0.539208,0.006241,0.125275,0.720040,0.589210,1.861306,2.267425,1.022079,2.133614,2.633323,2.153076,1.568749,2.116181,2.772545,2.811317,3.020836,3.002754,8.259827,8.354858,8.115745</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.425823,0.388393,0.206314,0.143143,0.570349,0.006636,0.133385,0.760739,0.622318,1.942502,2.355522,1.075873,2.220664,2.730813,2.241620,1.644908,2.206423,2.872508,2.913282,3.126189,3.107476,8.117766,8.211163,7.998960</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2.334282034131808</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>94.163284,94.000076,94.074532,94.238235,94.130081,94.048019,93.573677,93.860107,93.905708,93.797775,93.862640,93.555466,93.514832,93.686073,93.529251,93.603584,93.305077,93.307037,93.362488,93.261482,93.372383,93.230400,93.124649,92.942093</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>93.437912,93.127930,92.958939,93.065422,92.769691,92.797989,92.745003,92.485184,92.659584,92.433167,92.361786,92.368668,92.165474,91.876755,91.941833,91.852982,91.727951,91.645432,91.452698,91.419678,91.278961,91.051872,90.987717,90.952545</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:45</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>100.375427,100.038391,99.732407,99.624649,99.370834,99.466011,99.408920,99.089752,99.085907,98.844620,98.890991,98.853195,98.698128,98.651886,98.726036,98.560066,98.455902,98.384094,98.374794,98.257294,98.262337,98.072723,98.030045,97.991165</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>100.250565,99.884415,99.832916,99.557083,99.452629,99.328720,99.130219,99.046516,98.862381,98.803406,98.804382,98.403488,98.440247,98.584290,98.511734,98.748993,98.169930,98.109947,98.201584,98.089310,98.233505,98.231873,97.953094,97.791458</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>97.369995,96.553329,95.914780,95.724350,95.150352,95.061310,95.016876,94.453445,94.403564,94.051018,93.992706,93.775040,93.803459,93.628868,93.605888,93.680634,93.438789,93.373779,93.079163,92.866714,92.910858,92.618866,92.624969,92.549484</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>98.502991,97.848389,97.277382,97.116425,96.579933,96.622116,96.545586,96.059792,96.045441,95.672195,95.672157,95.615067,95.362411,95.213531,95.344238,95.314293,95.139084,95.005219,94.930313,94.938354,94.781342,94.464493,94.565392,94.453171</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>97.99116516113281</v>
+      </c>
+      <c r="G38" t="n">
+        <v>97.04000091552734</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9511642456054688</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9801774903459148</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9337545995138101</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:11</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="n">
+        <v>96.02443695068359</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>100.375427,100.038391,99.732407,99.624649,99.370834,99.466011,99.408920,99.089752,99.085907,98.844620,98.890991,98.853195,98.698128,98.651886,98.726036,98.560066,98.455902,98.384094,98.374794,98.257294,98.262337,98.072723,98.030045,97.991165</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>100.930000,101.599998,101.300003,101.870003,100.720001,100.199997,100.370003,99.790001,99.639999,98.589996,98.589996,97.120003,98.199997,98.379997,98.209999,98.199997,98.510002,97.970001,96.660004,97.169998,97.300003,96.639999,96.639999,97.040001</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.554573,1.561607,1.567596,2.245354,1.349167,0.733986,0.961083,0.700249,0.554092,0.254624,0.300995,1.733192,0.498131,0.271889,0.516037,0.360069,0.054100,0.414093,1.714790,1.087296,0.962334,1.432724,1.390046,0.951164</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.549463,1.537015,1.547479,2.204136,1.339523,0.732521,0.957540,0.701723,0.556094,0.258265,0.305299,1.784588,0.507262,0.276366,0.525442,0.366669,0.054918,0.422673,1.774043,1.118962,0.989038,1.482537,1.438375,0.980177</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9337545995138101</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>100.250565,99.884415,99.832916,99.557083,99.452629,99.328720,99.130219,99.046516,98.862381,98.803406,98.804382,98.403488,98.440247,98.584290,98.511734,98.748993,98.169930,98.109947,98.201584,98.089310,98.233505,98.231873,97.953094,97.791458</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>98.502991,97.848389,97.277382,97.116425,96.579933,96.622116,96.545586,96.059792,96.045441,95.672195,95.672157,95.615067,95.362411,95.213531,95.344238,95.314293,95.139084,95.005219,94.930313,94.938354,94.781342,94.464493,94.565392,94.453171</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:11</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>96.919472,96.723663,96.786041,96.768623,96.646561,96.692169,96.548820,96.338898,96.526443,96.466339,96.337517,96.380417,96.312538,96.218513,96.383842,96.263000,96.227074,96.175232,96.148827,96.190956,96.209930,96.054260,96.085617,96.024437</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>96.594627,96.631607,96.524673,96.771820,96.755692,96.604515,96.308334,96.157028,96.412704,96.424416,96.079994,96.036224,95.873367,96.141251,96.146393,96.145477,96.057861,95.892349,95.876541,95.977287,96.014755,95.824142,95.931488,95.705269</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>95.598724,95.304665,95.159721,95.231262,94.950165,94.903122,94.806396,94.441010,94.377052,94.097687,93.766937,93.829750,93.639923,93.516037,93.553085,93.499313,93.199577,93.017487,92.753067,92.671661,92.718307,92.387253,92.556915,92.500504</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>96.125244,95.732101,95.744164,95.714943,95.502426,95.588882,95.351227,95.024208,95.257614,94.983078,94.705803,94.824463,94.622009,94.438766,94.590981,94.476761,94.288902,94.108170,93.966942,94.132973,94.013824,93.742386,93.910294,93.852325</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>96.02443695068359</v>
+      </c>
+      <c r="G39" t="n">
+        <v>101.4700012207031</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.445564270019531</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.366674095307355</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.262247671247121</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:16</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="n">
+        <v>101.9984130859375</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>96.919472,96.723663,96.786041,96.768623,96.646561,96.692169,96.548820,96.338898,96.526443,96.466339,96.337517,96.380417,96.312538,96.218513,96.383842,96.263000,96.227074,96.175232,96.148827,96.190956,96.209930,96.054260,96.085617,96.024437</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>97.279999,97.040001,96.620003,97.070000,96.800003,96.930000,96.809998,96.180000,97.500000,97.019997,97.000000,96.550003,95.480003,95.940002,95.940002,96.959999,96.830002,96.800003,96.940002,98.269997,99.709999,102.099998,100.620003,101.470001</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.360527,0.316338,0.166038,0.301377,0.153442,0.237831,0.261178,0.158898,0.973557,0.553658,0.662483,0.169586,0.832535,0.278511,0.443840,0.696999,0.602928,0.624771,0.791175,2.079041,3.500069,6.045738,4.534386,5.445564</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.370607,0.325987,0.171847,0.310474,0.158515,0.245364,0.269784,0.165209,0.998520,0.570663,0.682972,0.175646,0.871947,0.290297,0.462622,0.718852,0.622666,0.645425,0.816150,2.115641,3.510249,5.921389,4.506446,5.366674</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1.262247671247121</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>96.594627,96.631607,96.524673,96.771820,96.755692,96.604515,96.308334,96.157028,96.412704,96.424416,96.079994,96.036224,95.873367,96.141251,96.146393,96.145477,96.057861,95.892349,95.876541,95.977287,96.014755,95.824142,95.931488,95.705269</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>96.125244,95.732101,95.744164,95.714943,95.502426,95.588882,95.351227,95.024208,95.257614,94.983078,94.705803,94.824463,94.622009,94.438766,94.590981,94.476761,94.288902,94.108170,93.966942,94.132973,94.013824,93.742386,93.910294,93.852325</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:16</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>104.285721,104.070564,104.266357,104.005066,103.685593,103.470245,103.658440,103.242706,103.314651,102.897682,103.151749,102.877075,103.054581,102.793991,103.059128,102.882881,102.898293,102.482796,102.510254,102.328384,102.310364,102.004456,102.036903,101.998413</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>104.140198,104.012695,104.310989,103.752411,103.656494,103.382217,103.371674,103.136353,103.061981,102.691544,102.905563,102.316040,102.682739,102.796295,102.855225,102.666794,102.570839,102.012711,102.187469,102.012283,101.997543,101.905502,102.009232,101.520721</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>101.739700,101.075714,100.856003,100.636383,99.802383,99.409439,99.491890,98.899529,98.676117,98.013840,98.074051,97.823120,97.866898,97.431053,97.670059,97.680344,97.365768,96.951599,96.673004,96.482101,96.502899,95.982750,96.228455,96.277863</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>102.724762,102.181343,102.069283,101.762001,101.068665,100.781395,100.865196,100.205750,100.321091,99.700851,99.780563,99.554245,99.547134,99.079620,99.390472,99.343033,99.121109,98.616638,98.590836,98.485992,98.358047,97.947556,98.179779,98.146317</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>101.9984130859375</v>
+      </c>
+      <c r="G40" t="n">
+        <v>106.0500030517578</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.051589965820312</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.820452474520845</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.857161886266471</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>105.4724884033203</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>104.285721,104.070564,104.266357,104.005066,103.685593,103.470245,103.658440,103.242706,103.314651,102.897682,103.151749,102.877075,103.054581,102.793991,103.059128,102.882881,102.898293,102.482796,102.510254,102.328384,102.310364,102.004456,102.036903,101.998413</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>104.389999,104.099998,103.940002,104.419998,106.089996,106.800003,107.199997,108.949997,108.199997,108.379997,109.440002,109.059998,108.769997,109.209999,109.180000,109.129997,107.879997,106.550003,106.870003,106.800003,107.250000,107.559998,106.360001,106.050003</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.104278,0.029434,0.326355,0.414932,2.404403,3.329758,3.541557,5.707291,4.885346,5.482315,6.288253,6.182923,5.715416,6.416008,6.120872,6.247116,4.981704,4.067207,4.359749,4.471619,4.939636,5.555542,4.323098,4.051590</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.099893,0.028275,0.313984,0.397368,2.266381,3.117751,3.303691,5.238450,4.515107,5.058420,5.745845,5.669285,5.254588,5.874927,5.606221,5.724472,4.617820,3.817182,4.079488,4.186909,4.605721,5.165063,4.064590,3.820453</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3.857161886266471</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>104.140198,104.012695,104.310989,103.752411,103.656494,103.382217,103.371674,103.136353,103.061981,102.691544,102.905563,102.316040,102.682739,102.796295,102.855225,102.666794,102.570839,102.012711,102.187469,102.012283,101.997543,101.905502,102.009232,101.520721</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>102.724762,102.181343,102.069283,101.762001,101.068665,100.781395,100.865196,100.205750,100.321091,99.700851,99.780563,99.554245,99.547134,99.079620,99.390472,99.343033,99.121109,98.616638,98.590836,98.485992,98.358047,97.947556,98.179779,98.146317</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>106.569389,106.306732,106.369408,106.400208,106.139069,106.196396,106.333908,106.196564,106.340858,106.157112,106.210587,106.146614,106.081802,105.910294,105.967102,105.870735,105.834137,105.655846,105.445938,105.524277,105.649002,105.247192,105.408653,105.472488</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>106.451263,106.431610,106.317612,106.516762,106.076950,105.963043,106.107574,105.915024,106.037674,105.910309,105.889023,105.858154,105.679291,105.944702,105.619156,105.748055,105.724091,105.031662,105.136803,105.060669,105.175835,104.985687,105.012146,104.966911</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>105.594170,105.174866,104.875694,104.902756,104.322601,104.119980,104.045906,103.681717,103.545609,103.055656,102.900955,102.761261,102.544189,102.039543,101.956436,101.881630,101.534439,101.266594,100.560112,100.512558,100.583794,99.892853,100.029015,100.092598</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>106.016159,105.605392,105.446991,105.361008,104.813629,104.811249,104.872025,104.470596,104.576950,104.151413,104.086349,104.033272,103.812393,103.349457,103.332474,103.413620,103.072220,102.750999,102.374062,102.500137,102.378860,101.785553,101.977905,102.058014</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>105.4724884033203</v>
+      </c>
+      <c r="G41" t="n">
+        <v>103.6100006103516</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.862487792968736</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.797594616346964</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.769643646205908</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:47</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="n">
+        <v>102.8656921386719</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>106.569389,106.306732,106.369408,106.400208,106.139069,106.196396,106.333908,106.196564,106.340858,106.157112,106.210587,106.146614,106.081802,105.910294,105.967102,105.870735,105.834137,105.655846,105.445938,105.524277,105.649002,105.247192,105.408653,105.472488</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>104.900002,105.519997,106.290001,105.290001,105.180000,104.699997,103.019997,103.379997,103.860001,103.419998,104.150002,104.150002,103.900002,104.169998,103.940002,103.870003,103.879997,104.029999,103.610001,103.610001,103.610001,103.610001,103.610001,103.610001</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1.669387,0.786735,0.079407,1.110207,0.959069,1.496399,3.313911,2.816567,2.480857,2.737114,2.060585,1.996612,2.181800,1.740296,2.027100,2.000732,1.954140,1.625847,1.835937,1.914276,2.039001,1.637191,1.798652,1.862487</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1.591408,0.745579,0.074708,1.054428,0.911836,1.429225,3.216765,2.724479,2.388655,2.646600,1.978479,1.917055,2.099904,1.670631,1.950259,1.926189,1.881151,1.562864,1.771969,1.847579,1.967958,1.580148,1.735983,1.797594</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1.769643646205908</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>106.451263,106.431610,106.317612,106.516762,106.076950,105.963043,106.107574,105.915024,106.037674,105.910309,105.889023,105.858154,105.679291,105.944702,105.619156,105.748055,105.724091,105.031662,105.136803,105.060669,105.175835,104.985687,105.012146,104.966911</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>106.016159,105.605392,105.446991,105.361008,104.813629,104.811249,104.872025,104.470596,104.576950,104.151413,104.086349,104.033272,103.812393,103.349457,103.332474,103.413620,103.072220,102.750999,102.374062,102.500137,102.378860,101.785553,101.977905,102.058014</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:47</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>103.743927,103.546608,103.561150,103.538063,103.428673,103.439606,103.577438,103.331848,103.497162,103.328972,103.245354,103.228470,103.230057,103.074066,103.192291,103.140274,103.083687,102.979553,103.023270,102.959816,103.043671,102.838005,102.856110,102.865692</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>103.780533,103.500381,103.561340,103.481743,103.548538,103.389542,102.985657,103.135468,103.341545,103.126907,103.020706,102.773491,103.005928,103.074677,102.917076,102.918556,102.957069,102.723152,102.789810,102.528824,102.705910,102.606430,102.579422,102.468384</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>102.806625,102.493591,102.072357,102.036804,101.616974,101.365326,101.511368,101.137390,101.041855,100.615112,100.351616,100.331436,100.203568,99.839233,99.875847,99.848206,99.625854,99.416565,99.060455,98.858650,98.765205,98.310204,98.339752,98.395264</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>103.247284,102.949677,102.729530,102.553894,102.064308,102.106804,102.187218,101.799660,101.957825,101.580315,101.293732,101.264420,101.282867,100.866165,101.006302,101.088013,100.751907,100.609375,100.518654,100.432518,100.330597,99.891411,100.089111,100.061287</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>102.8656921386719</v>
+      </c>
+      <c r="G42" t="n">
+        <v>105.2200012207031</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.354309082031222</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.237510981484371</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.442628859656955</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="n">
+        <v>105.2009887695312</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>103.743927,103.546608,103.561150,103.538063,103.428673,103.439606,103.577438,103.331848,103.497162,103.328972,103.245354,103.228470,103.230057,103.074066,103.192291,103.140274,103.083687,102.979553,103.023270,102.959816,103.043671,102.838005,102.856110,102.865692</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>103.750000,103.480003,103.339996,103.459999,103.510002,103.629997,103.820000,105.360001,105.019997,104.879997,104.879997,105.129997,105.370003,105.230003,105.040001,105.519997,105.610001,105.279999,105.250000,105.239998,105.070000,105.129997,105.220001,105.220001</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.006073,0.066605,0.221154,0.078064,0.081329,0.190391,0.242562,2.028153,1.522835,1.551025,1.634643,1.901527,2.139946,2.155937,1.847710,2.379723,2.526314,2.300446,2.226730,2.280182,2.026329,2.291992,2.363891,2.354309</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.005853,0.064365,0.214006,0.075453,0.078571,0.183722,0.233637,1.924974,1.450043,1.478857,1.558584,1.808739,2.030887,2.048786,1.759054,2.255234,2.392116,2.185074,2.115658,2.166649,1.928551,2.180151,2.246618,2.237511</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1.442628859656955</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>103.780533,103.500381,103.561340,103.481743,103.548538,103.389542,102.985657,103.135468,103.341545,103.126907,103.020706,102.773491,103.005928,103.074677,102.917076,102.918556,102.957069,102.723152,102.789810,102.528824,102.705910,102.606430,102.579422,102.468384</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>103.247284,102.949677,102.729530,102.553894,102.064308,102.106804,102.187218,101.799660,101.957825,101.580315,101.293732,101.264420,101.282867,100.866165,101.006302,101.088013,100.751907,100.609375,100.518654,100.432518,100.330597,99.891411,100.089111,100.061287</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>105.255447,105.072403,105.185501,105.230026,105.161087,105.184357,105.308029,105.178329,105.300873,105.210739,105.184418,105.317924,105.238579,105.139534,105.297897,105.247711,105.222046,105.084259,105.190781,105.116135,105.193199,105.136200,105.070549,105.200989</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>105.215805,104.965073,105.099167,105.221161,105.447052,105.011337,104.853302,104.969292,105.142365,105.058098,105.036407,104.931892,105.119781,105.463715,105.115341,105.024345,105.026062,104.912201,105.092789,104.812378,104.867958,104.576561,104.947021,104.813202</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>104.336380,104.048569,103.946312,104.029945,103.680695,103.483574,103.713028,103.551216,103.327263,103.046600,102.863808,103.076477,102.824692,102.526810,102.531174,102.483780,102.324493,102.031204,101.751022,101.458717,101.545326,101.277985,101.162048,101.254288</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>104.879822,104.573708,104.530853,104.542374,104.134323,104.136215,104.191452,104.036118,104.150536,103.935989,103.727066,103.895172,103.883255,103.457077,103.553589,103.501312,103.434631,103.059898,103.022354,102.909454,102.859421,102.685608,102.700699,102.855225</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>105.2009887695312</v>
+      </c>
+      <c r="G43" t="n">
+        <v>101.5999984741211</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.600990295410099</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.544281840050736</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.559876856512461</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>100.8134460449219</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>105.255447,105.072403,105.185501,105.230026,105.161087,105.184357,105.308029,105.178329,105.300873,105.210739,105.184418,105.317924,105.238579,105.139534,105.297897,105.247711,105.222046,105.084259,105.190781,105.116135,105.193199,105.136200,105.070549,105.200989</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>105.419998,104.820000,104.750000,104.610001,105.110001,105.120003,106.099998,107.120003,106.739998,106.269997,106.910004,106.389999,106.680000,105.820000,104.760002,104.459999,103.790001,101.760002,102.139999,101.510002,101.440002,101.949997,101.440002,101.599998</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.164551,0.252403,0.435501,0.620025,0.051086,0.064354,0.791969,1.941674,1.439125,1.059258,1.725586,1.072075,1.441421,0.680466,0.537895,0.787712,1.432045,3.324257,3.050782,3.606133,3.753197,3.186203,3.630547,3.600991</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.156091,0.240797,0.415753,0.592702,0.048603,0.061220,0.746437,1.812615,1.348253,0.996761,1.614054,1.007684,1.351164,0.643041,0.513454,0.754080,1.379752,3.266762,2.986863,3.552490,3.699918,3.125261,3.579009,3.544282</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1.559876856512461</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>105.215805,104.965073,105.099167,105.221161,105.447052,105.011337,104.853302,104.969292,105.142365,105.058098,105.036407,104.931892,105.119781,105.463715,105.115341,105.024345,105.026062,104.912201,105.092789,104.812378,104.867958,104.576561,104.947021,104.813202</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>104.879822,104.573708,104.530853,104.542374,104.134323,104.136215,104.191452,104.036118,104.150536,103.935989,103.727066,103.895172,103.883255,103.457077,103.553589,103.501312,103.434631,103.059898,103.022354,102.909454,102.859421,102.685608,102.700699,102.855225</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>101.547729,101.374268,101.347900,101.271210,101.154678,101.156128,101.187698,101.142273,101.157928,101.102486,101.137138,101.125473,101.082062,100.927536,101.032791,100.938904,100.790298,100.698898,100.819092,100.671555,100.736496,100.733398,100.721069,100.813446</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>101.343124,101.200096,101.330086,101.408180,101.231033,101.142075,101.056046,100.977364,100.867462,101.116676,101.036964,101.053940,101.003227,101.121048,100.987213,100.922363,100.686356,100.643219,100.980034,100.555710,100.722099,100.324318,100.833908,100.559723</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>100.325165,100.002670,99.732285,99.727829,99.290459,99.067848,99.009476,98.836639,98.482544,98.154938,98.047592,98.006119,97.759499,97.387924,97.344055,97.319145,96.981461,96.830627,96.511551,96.219666,96.228317,96.127174,96.060883,95.923126</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>100.911148,100.580666,100.375313,100.327606,99.916145,99.852913,99.685913,99.516716,99.533157,99.314316,99.144463,99.043953,98.984161,98.560135,98.585808,98.591904,98.268982,98.124405,98.076920,97.969864,97.868294,97.707817,97.788483,97.822723</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>100.8134460449219</v>
+      </c>
+      <c r="G44" t="n">
+        <v>103.7399978637695</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.926551818847628</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.821044803462162</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.206398734224448</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="n">
+        <v>104.1518402099609</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>101.547729,101.374268,101.347900,101.271210,101.154678,101.156128,101.187698,101.142273,101.157928,101.102486,101.137138,101.125473,101.082062,100.927536,101.032791,100.938904,100.790298,100.698898,100.819092,100.671555,100.736496,100.733398,100.721069,100.813446</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>102.709999,102.980003,103.230003,103.070000,103.650002,103.379997,102.750000,102.320000,103.480003,102.870003,102.820000,103.610001,104.459999,103.620003,103.720001,103.639999,103.199997,103.050003,103.169998,103.230003,103.370003,103.620003,103.739998,103.739998</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.162270,1.605735,1.882103,1.798790,2.495324,2.223869,1.562302,1.177727,2.322075,1.767517,1.682862,2.484528,3.377937,2.692467,2.687210,2.701095,2.409699,2.351105,2.350906,2.558448,2.633507,2.886605,3.018929,2.926552</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.131604,1.559269,1.823213,1.745212,2.407452,2.151160,1.520489,1.151023,2.243985,1.718204,1.636707,2.397961,3.233713,2.598404,2.590831,2.606229,2.334980,2.281519,2.278672,2.478396,2.547651,2.785760,2.910092,2.821045</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>2.206398734224448</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>101.343124,101.200096,101.330086,101.408180,101.231033,101.142075,101.056046,100.977364,100.867462,101.116676,101.036964,101.053940,101.003227,101.121048,100.987213,100.922363,100.686356,100.643219,100.980034,100.555710,100.722099,100.324318,100.833908,100.559723</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>100.911148,100.580666,100.375313,100.327606,99.916145,99.852913,99.685913,99.516716,99.533157,99.314316,99.144463,99.043953,98.984161,98.560135,98.585808,98.591904,98.268982,98.124405,98.076920,97.969864,97.868294,97.707817,97.788483,97.822723</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>103.750351,103.822945,103.960724,104.096886,104.014816,104.065674,104.169388,104.189568,104.142227,104.125259,104.160744,104.185822,104.178604,104.105263,104.232712,104.225441,104.154587,104.081818,104.086838,104.030174,104.020004,104.070740,104.063736,104.151840</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>103.595543,103.834152,104.025047,104.013580,104.213409,104.112083,104.049835,104.040787,103.822235,104.044861,104.165649,103.894867,104.236305,104.303604,104.153992,103.960388,104.009659,104.271515,104.373070,103.978180,104.042900,103.781624,104.153847,103.997650</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>102.434052,102.534531,102.449730,102.625443,102.414352,102.201248,102.403625,102.296951,102.114517,101.926643,101.847473,101.691071,101.569077,101.436859,101.465057,101.401062,101.203926,101.050133,100.753098,100.484070,100.466171,100.391922,100.361374,100.332108</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>103.071289,103.094681,103.089920,103.231087,102.932106,102.914307,103.049744,103.022041,102.997948,102.820572,102.668823,102.644272,102.620239,102.290222,102.427612,102.450790,102.232101,102.071098,101.998535,101.933075,101.842529,101.695885,101.802597,101.828018</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>104.1518402099609</v>
+      </c>
+      <c r="G45" t="n">
+        <v>99.84999847412109</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.301841735839801</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.308304257966256</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.040126874414202</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="n">
+        <v>99.68881225585938</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>103.750351,103.822945,103.960724,104.096886,104.014816,104.065674,104.169388,104.189568,104.142227,104.125259,104.160744,104.185822,104.178604,104.105263,104.232712,104.225441,104.154587,104.081818,104.086838,104.030174,104.020004,104.070740,104.063736,104.151840</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>104.290001,103.360001,103.129997,102.040001,101.949997,102.349998,102.260002,101.910004,101.930000,101.970001,102.000000,100.889999,100.570000,99.580002,100.029999,100.059998,99.550003,99.620003,99.730003,99.620003,99.059998,99.889999,100.250000,99.849998</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.539650,0.462944,0.830727,2.056885,2.064819,1.715676,1.909386,2.279564,2.212227,2.155258,2.160744,3.295823,3.608604,4.525261,4.202713,4.165443,4.604584,4.461815,4.356835,4.410171,4.960006,4.180741,3.813736,4.301842</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.517451,0.447895,0.805514,2.015763,2.025325,1.676283,1.867187,2.236841,2.170339,2.113619,2.118376,3.266749,3.588152,4.544347,4.201453,4.162946,4.625398,4.478835,4.368630,4.426994,5.007073,4.185345,3.804225,4.308304</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>3.040126874414202</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>103.595543,103.834152,104.025047,104.013580,104.213409,104.112083,104.049835,104.040787,103.822235,104.044861,104.165649,103.894867,104.236305,104.303604,104.153992,103.960388,104.009659,104.271515,104.373070,103.978180,104.042900,103.781624,104.153847,103.997650</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>103.071289,103.094681,103.089920,103.231087,102.932106,102.914307,103.049744,103.022041,102.997948,102.820572,102.668823,102.644272,102.620239,102.290222,102.427612,102.450790,102.232101,102.071098,101.998535,101.933075,101.842529,101.695885,101.802597,101.828018</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>99.731232,99.779823,99.825455,99.813583,99.688965,99.691879,99.777405,99.711319,99.736198,99.769104,99.740082,99.742233,99.778969,99.748199,99.749428,99.730431,99.656769,99.591179,99.679703,99.505188,99.489517,99.589951,99.598129,99.688812</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>99.579399,99.743286,99.787140,99.818909,99.829941,99.790192,99.837021,99.495964,99.692734,99.888039,99.780090,99.814308,99.998405,99.951790,99.888504,99.521019,99.747337,99.892380,100.040604,99.774399,99.742294,99.370331,99.697113,99.928055</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>98.843819,98.820068,98.614975,98.721542,98.338318,98.138260,98.273239,98.137306,97.869011,97.735214,97.492630,97.369980,97.283707,97.184906,97.099464,97.003632,96.789337,96.582008,96.266716,96.067505,96.077011,96.144989,96.105423,96.108482</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>99.306252,99.211456,99.157883,99.095985,98.792725,98.746178,98.691086,98.600418,98.700081,98.503845,98.305290,98.160851,98.234413,98.055725,98.037743,97.982132,97.791748,97.499664,97.541412,97.441315,97.335144,97.366920,97.411804,97.462280</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>99.68881225585938</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100.5500030517578</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.8611907958984375</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.8564801290509581</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7102439225024038</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:06:59</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="n">
+        <v>99.88468933105469</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>99.731232,99.779823,99.825455,99.813583,99.688965,99.691879,99.777405,99.711319,99.736198,99.769104,99.740082,99.742233,99.778969,99.748199,99.749428,99.730431,99.656769,99.591179,99.679703,99.505188,99.489517,99.589951,99.598129,99.688812</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>100.230003,100.050003,99.800003,98.940002,98.599998,98.169998,98.070000,97.650002,99.160004,98.889999,99.250000,98.750000,99.260002,99.489998,99.379997,99.660004,99.629997,99.510002,100.400002,99.489998,100.139999,101.050003,100.480003,100.550003</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.498771,0.270180,0.025452,0.873581,1.088967,1.521881,1.707405,2.061317,0.576194,0.879105,0.490082,0.992233,0.518967,0.258201,0.369431,0.070427,0.026772,0.081177,0.720299,0.015190,0.650482,1.460052,0.881874,0.861191</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.497627,0.270045,0.025503,0.882940,1.104429,1.550250,1.741007,2.110924,0.581075,0.888972,0.493785,1.004793,0.522836,0.259525,0.371736,0.070668,0.026871,0.081577,0.717429,0.015268,0.649573,1.444881,0.877662,0.856480</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7102439225024038</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>99.579399,99.743286,99.787140,99.818909,99.829941,99.790192,99.837021,99.495964,99.692734,99.888039,99.780090,99.814308,99.998405,99.951790,99.888504,99.521019,99.747337,99.892380,100.040604,99.774399,99.742294,99.370331,99.697113,99.928055</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>99.306252,99.211456,99.157883,99.095985,98.792725,98.746178,98.691086,98.600418,98.700081,98.503845,98.305290,98.160851,98.234413,98.055725,98.037743,97.982132,97.791748,97.499664,97.541412,97.441315,97.335144,97.366920,97.411804,97.462280</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:06:59</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>100.632904,100.573006,100.523056,100.561256,100.413353,100.344574,100.401299,100.351860,100.306419,100.261246,100.173065,100.142761,100.145493,100.059174,100.106018,100.128479,100.093613,99.945961,100.011078,99.833054,99.874802,99.819443,99.713852,99.884689</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>100.492500,100.401978,100.559631,100.465088,100.502686,100.385178,100.304260,100.029190,100.073883,100.255524,100.070435,100.036926,100.058571,100.180344,100.050438,99.909492,99.903976,99.933136,100.045197,99.869072,99.835236,99.571304,99.772400,99.785797</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>99.534035,99.394119,99.017883,99.148483,98.797150,98.535248,98.560822,98.466866,98.196274,97.978577,97.715286,97.538132,97.449219,97.248611,97.278931,97.221794,97.027855,96.818436,96.453064,96.296814,96.410278,96.297318,96.181000,96.230057</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>100.048676,99.844460,99.662178,99.659019,99.319656,99.194534,99.171379,99.087387,99.135468,98.922165,98.656982,98.468201,98.461365,98.195694,98.285706,98.338882,98.124741,97.832077,97.771866,97.705750,97.681198,97.532196,97.515762,97.644135</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>99.88468933105469</v>
+      </c>
+      <c r="G47" t="n">
+        <v>103.629997253418</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.745307922363281</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.614115624460033</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.810963501049056</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:38</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="n">
+        <v>102.4367370605469</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>100.632904,100.573006,100.523056,100.561256,100.413353,100.344574,100.401299,100.351860,100.306419,100.261246,100.173065,100.142761,100.145493,100.059174,100.106018,100.128479,100.093613,99.945961,100.011078,99.833054,99.874802,99.819443,99.713852,99.884689</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>100.820000,100.839996,100.360001,100.589996,100.129997,100.410004,100.760002,101.650002,101.459999,104.800003,105.160004,104.550003,105.099998,105.209999,105.290001,104.930000,105.220001,104.169998,103.940002,103.480003,103.800003,103.790001,103.709999,103.629997</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.187096,0.266990,0.163055,0.028740,0.283356,0.065430,0.358703,1.298142,1.153580,4.538757,4.986939,4.407242,4.954505,5.150825,5.183983,4.801521,5.126388,4.224037,3.928924,3.646949,3.925201,3.970558,3.996147,3.745308</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.185574,0.264766,0.162470,0.028572,0.282988,0.065162,0.355998,1.277070,1.136980,4.330875,4.742239,4.215439,4.714087,4.895756,4.923528,4.575928,4.872066,4.054946,3.779993,3.524303,3.781504,3.825569,3.853194,3.614116</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2.810963501049056</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>100.492500,100.401978,100.559631,100.465088,100.502686,100.385178,100.304260,100.029190,100.073883,100.255524,100.070435,100.036926,100.058571,100.180344,100.050438,99.909492,99.903976,99.933136,100.045197,99.869072,99.835236,99.571304,99.772400,99.785797</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>100.048676,99.844460,99.662178,99.659019,99.319656,99.194534,99.171379,99.087387,99.135468,98.922165,98.656982,98.468201,98.461365,98.195694,98.285706,98.338882,98.124741,97.832077,97.771866,97.705750,97.681198,97.532196,97.515762,97.644135</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:38</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>103.809914,103.736526,103.685242,103.723618,103.634766,103.520020,103.588509,103.636871,103.582100,103.457764,103.492226,103.471680,103.434036,103.270004,103.286667,103.211891,103.113632,102.933350,102.804840,102.699371,102.620224,102.573105,102.403290,102.436737</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>103.616737,103.627167,103.778214,103.575569,103.676376,103.554825,103.561188,103.561371,103.170547,103.432755,103.465355,103.420654,103.261154,103.386208,103.294884,102.921776,102.891533,102.756271,102.653915,102.508194,102.542656,102.482361,102.355331,102.282822</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>102.581612,102.578232,102.254578,102.344032,102.011002,101.700333,101.635040,101.565674,101.295715,101.035004,100.881302,100.685577,100.585907,100.108124,100.109253,99.906731,99.597870,99.321487,98.775787,98.649261,98.520203,98.318878,98.174194,98.033073</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>103.124847,103.027397,102.837234,102.859009,102.510406,102.303055,102.324776,102.248405,102.264473,101.966942,101.836929,101.661453,101.571724,101.171104,101.253418,101.180267,100.923126,100.565140,100.293442,100.255737,100.081451,99.830818,99.782700,99.710175</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>102.4367370605469</v>
+      </c>
+      <c r="G48" t="n">
+        <v>101.8199996948242</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.6167373657226847</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6057133839826903</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.084802628352761</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:35</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
+        <v>101.73291015625</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>103.809914,103.736526,103.685242,103.723618,103.634766,103.520020,103.588509,103.636871,103.582100,103.457764,103.492226,103.471680,103.434036,103.270004,103.286667,103.211891,103.113632,102.933350,102.804840,102.699371,102.620224,102.573105,102.403290,102.436737</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>103.699997,103.620003,103.599998,104.370003,104.040001,104.139999,104.080002,101.580002,101.660004,100.779999,101.449997,101.820000,101.250000,101.660004,101.709999,101.779999,101.610001,101.769997,101.940002,101.839996,101.870003,101.970001,101.889999,101.820000</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.109917,0.116523,0.085244,0.646385,0.405235,0.619979,0.491493,2.056869,1.922096,2.677765,2.042229,1.651680,2.184036,1.610000,1.576668,1.431892,1.503631,1.163353,0.864838,0.859375,0.750221,0.603104,0.513291,0.616737</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.105995,0.112452,0.082281,0.619320,0.389499,0.595333,0.472226,2.024876,1.890710,2.657040,2.013040,1.622157,2.157073,1.583711,1.550160,1.406850,1.479806,1.143120,0.848379,0.843848,0.736450,0.591452,0.503769,0.605713</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.084802628352761</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>103.616737,103.627167,103.778214,103.575569,103.676376,103.554825,103.561188,103.561371,103.170547,103.432755,103.465355,103.420654,103.261154,103.386208,103.294884,102.921776,102.891533,102.756271,102.653915,102.508194,102.542656,102.482361,102.355331,102.282822</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>103.124847,103.027397,102.837234,102.859009,102.510406,102.303055,102.324776,102.248405,102.264473,101.966942,101.836929,101.661453,101.571724,101.171104,101.253418,101.180267,100.923126,100.565140,100.293442,100.255737,100.081451,99.830818,99.782700,99.710175</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:35</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>101.895584,101.932266,101.899261,101.962624,101.988838,101.915077,101.892365,101.945763,101.851700,101.753403,101.738480,101.729538,101.687805,101.622894,101.698547,101.785385,101.736809,101.682053,101.667801,101.652939,101.776917,101.697800,101.556259,101.732910</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>101.663177,102.117088,101.851486,101.945786,102.240883,101.820526,101.928734,101.620010,101.539154,101.763336,101.754761,101.660812,101.777634,101.785797,101.636528,101.664162,101.828049,101.837494,101.801559,101.644485,101.671371,101.803223,101.848160,101.609253</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>101.039413,101.268898,101.083557,101.109039,100.917007,100.708031,100.643829,100.644577,100.276001,100.038330,99.964951,99.617622,99.533920,99.201996,99.343819,99.423264,99.249420,99.170074,98.747849,98.598373,98.722229,98.570442,98.529930,98.557983</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>101.402664,101.493866,101.382042,101.364502,101.279121,101.083878,101.148232,101.152267,101.056274,100.796570,100.511383,100.375710,100.276337,100.046524,100.231171,100.359261,100.131897,100.051071,99.896439,99.888252,99.988350,99.648979,99.692413,99.772499</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>101.73291015625</v>
+      </c>
+      <c r="G49" t="n">
+        <v>106.1100006103516</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.377090454101562</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.125049881183919</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.515655417130963</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="n">
+        <v>105.5290985107422</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>101.895584,101.932266,101.899261,101.962624,101.988838,101.915077,101.892365,101.945763,101.851700,101.753403,101.738480,101.729538,101.687805,101.622894,101.698547,101.785385,101.736809,101.682053,101.667801,101.652939,101.776917,101.697800,101.556259,101.732910</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>101.889999,102.309998,102.250000,102.580002,102.540001,102.540001,102.339996,103.239998,102.660004,102.879997,102.959999,103.419998,104.260002,103.919998,103.419998,103.250000,103.739998,103.379997,103.260002,103.300003,104.059998,104.370003,105.970001,106.110001</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.005585,0.377732,0.350739,0.617378,0.551163,0.624924,0.447631,1.294235,0.808304,1.126594,1.221519,1.690460,2.572197,2.297104,1.721451,1.464615,2.003189,1.697944,1.592201,1.647064,2.283081,2.672203,4.413742,4.377091</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.005481,0.369203,0.343021,0.601850,0.537510,0.609444,0.437396,1.253618,0.787360,1.095057,1.186402,1.634558,2.467099,2.210454,1.664524,1.418513,1.930971,1.642430,1.541934,1.594447,2.194004,2.560317,4.165087,4.125050</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1.515655417130963</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>101.663177,102.117088,101.851486,101.945786,102.240883,101.820526,101.928734,101.620010,101.539154,101.763336,101.754761,101.660812,101.777634,101.785797,101.636528,101.664162,101.828049,101.837494,101.801559,101.644485,101.671371,101.803223,101.848160,101.609253</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>101.402664,101.493866,101.382042,101.364502,101.279121,101.083878,101.148232,101.152267,101.056274,100.796570,100.511383,100.375710,100.276337,100.046524,100.231171,100.359261,100.131897,100.051071,99.896439,99.888252,99.988350,99.648979,99.692413,99.772499</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>105.888786,105.903252,105.814499,105.782623,105.637695,105.531921,105.506958,105.430740,105.438873,105.329315,105.324333,105.380417,105.355774,105.270050,105.283417,105.404778,105.420303,105.267670,105.406326,105.404373,105.472473,105.450974,105.466599,105.529099</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>105.541870,105.750824,105.854034,105.566589,105.769806,105.476791,105.436356,105.306313,105.196022,105.345490,105.291061,105.021866,105.312714,105.242249,104.989342,105.472290,105.296120,105.147026,105.567596,105.320251,105.186905,105.650856,105.659546,105.499168</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>104.346680,104.310577,103.997490,104.041092,103.690163,103.388397,103.317902,103.243637,102.915192,102.692642,102.532410,102.417717,102.305298,102.125160,102.086487,102.341431,102.227097,102.068558,101.902756,101.928192,101.988754,101.844055,101.861931,101.814926</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>104.983017,104.955902,104.757721,104.691025,104.371979,104.209938,104.103447,104.040192,104.042938,103.750198,103.569672,103.489838,103.435074,103.293274,103.335892,103.560745,103.470459,103.187134,103.266121,103.348236,103.391998,103.096024,103.161453,103.257126</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>105.5290985107422</v>
+      </c>
+      <c r="G50" t="n">
+        <v>105.0199966430664</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.5091018676757955</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4847666005990177</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6316977254234457</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:46</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>104.3627166748047</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>105.888786,105.903252,105.814499,105.782623,105.637695,105.531921,105.506958,105.430740,105.438873,105.329315,105.324333,105.380417,105.355774,105.270050,105.283417,105.404778,105.420303,105.267670,105.406326,105.404373,105.472473,105.450974,105.466599,105.529099</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>106.370003,105.379997,105.290001,105.199997,106.500000,106.680000,106.459999,106.800003,107.080002,105.720001,105.739998,106.080002,106.199997,105.989998,105.489998,105.690002,105.919998,105.849998,106.559998,106.150002,105.330002,105.750000,104.949997,105.019997</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.481217,0.523255,0.524498,0.582626,0.862305,1.148079,0.953041,1.369263,1.641129,0.390686,0.415665,0.699585,0.844223,0.719948,0.206581,0.285224,0.499695,0.582328,1.153672,0.745629,0.142471,0.299026,0.516602,0.509102</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.452399,0.496541,0.498146,0.553827,0.809676,1.076190,0.895210,1.282081,1.532619,0.369548,0.393101,0.659488,0.794937,0.679260,0.195830,0.269869,0.471767,0.550145,1.082650,0.702429,0.135262,0.282767,0.492236,0.484767</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6316977254234457</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>105.541870,105.750824,105.854034,105.566589,105.769806,105.476791,105.436356,105.306313,105.196022,105.345490,105.291061,105.021866,105.312714,105.242249,104.989342,105.472290,105.296120,105.147026,105.567596,105.320251,105.186905,105.650856,105.659546,105.499168</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>104.983017,104.955902,104.757721,104.691025,104.371979,104.209938,104.103447,104.040192,104.042938,103.750198,103.569672,103.489838,103.435074,103.293274,103.335892,103.560745,103.470459,103.187134,103.266121,103.348236,103.391998,103.096024,103.161453,103.257126</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:46</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>104.998978,104.899742,104.809372,104.867493,104.768456,104.725586,104.678757,104.744743,104.751312,104.581390,104.619438,104.626122,104.506523,104.368469,104.474213,104.451378,104.471924,104.476837,104.495682,104.442787,104.444046,104.366608,104.219528,104.362717</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>104.709892,104.743378,104.815277,104.825897,104.758316,104.755859,104.468643,104.729424,104.322922,104.636993,104.574722,104.439911,104.227905,104.320267,104.233070,104.446075,104.215942,104.173470,104.282799,104.386780,104.160477,104.426590,104.170837,104.154144</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>103.826263,103.729218,103.332443,103.355301,103.129471,102.770836,102.590469,102.589844,102.367004,102.049347,101.856659,101.820908,101.600281,101.311485,101.255920,101.231316,101.093536,101.027451,100.710495,100.618988,100.525543,100.444740,100.179916,100.180618</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>104.338539,104.160385,103.935333,103.925346,103.644379,103.459435,103.358063,103.324570,103.423325,103.108261,102.903809,102.812889,102.634064,102.413727,102.518112,102.541306,102.383667,102.270531,102.182823,102.185257,102.159546,101.756638,101.649841,101.750916</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>104.3627166748047</v>
+      </c>
+      <c r="G51" t="n">
+        <v>103.1100006103516</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.252716064453139</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.214931681735801</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.4956402102555956</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="n">
+        <v>102.8853225708008</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>104.998978,104.899742,104.809372,104.867493,104.768456,104.725586,104.678757,104.744743,104.751312,104.581390,104.619438,104.626122,104.506523,104.368469,104.474213,104.451378,104.471924,104.476837,104.495682,104.442787,104.444046,104.366608,104.219528,104.362717</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>105.139999,105.050003,104.470001,104.699997,104.650002,105.000000,104.919998,105.730003,105.089996,104.650002,103.220001,103.860001,103.989998,103.910004,104.370003,104.080002,103.889999,103.529999,103.790001,104.080002,104.349998,103.279999,103.330002,103.110001</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.141021,0.150261,0.339371,0.167496,0.118454,0.274414,0.241241,0.985260,0.338684,0.068612,1.399437,0.766121,0.516525,0.458465,0.104210,0.371376,0.581925,0.946838,0.705681,0.362785,0.094048,1.086609,0.889526,1.252716</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.134127,0.143038,0.324850,0.159977,0.113191,0.261347,0.229929,0.931864,0.322280,0.065563,1.355781,0.737648,0.496707,0.441214,0.099847,0.356818,0.560135,0.914554,0.679912,0.348564,0.090127,1.052100,0.860860,1.214932</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.4956402102555956</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>104.709892,104.743378,104.815277,104.825897,104.758316,104.755859,104.468643,104.729424,104.322922,104.636993,104.574722,104.439911,104.227905,104.320267,104.233070,104.446075,104.215942,104.173470,104.282799,104.386780,104.160477,104.426590,104.170837,104.154144</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>104.338539,104.160385,103.935333,103.925346,103.644379,103.459435,103.358063,103.324570,103.423325,103.108261,102.903809,102.812889,102.634064,102.413727,102.518112,102.541306,102.383667,102.270531,102.182823,102.185257,102.159546,101.756638,101.649841,101.750916</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>103.092346,102.982117,102.924789,102.930710,102.841331,102.856621,102.923431,102.889587,102.891350,102.840195,102.860886,102.934158,102.863235,102.804977,102.893356,102.917046,102.905464,102.896652,102.912903,102.958374,102.988159,102.977318,102.835876,102.885323</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>102.850006,103.001793,102.882187,102.953857,103.010109,102.954994,102.956055,102.803436,102.729073,102.867523,102.563370,102.826202,102.891640,102.956627,102.801498,102.794235,102.947815,102.855148,103.068649,102.852310,102.778534,102.804489,102.786896,102.882751</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>102.269882,102.205673,101.918335,101.940758,101.604950,101.428223,101.440842,101.257011,101.017746,100.848763,100.710884,100.716843,100.450699,100.311478,100.354172,100.294357,100.145889,100.065430,99.705551,99.768585,99.681488,99.757202,99.521935,99.423828</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>102.640640,102.470566,102.294830,102.227188,102.050247,101.932602,101.898399,101.805710,101.897102,101.667648,101.490524,101.541245,101.412605,101.248840,101.401230,101.339493,101.184113,101.120262,101.034248,101.124985,101.133041,101.002419,100.854523,100.834518</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>102.8853225708008</v>
+      </c>
+      <c r="G52" t="n">
+        <v>103.7699966430664</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.8846740722656108</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8525335847399028</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.480141330567365</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="n">
+        <v>103.5565948486328</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>103.092346,102.982117,102.924789,102.930710,102.841331,102.856621,102.923431,102.889587,102.891350,102.840195,102.860886,102.934158,102.863235,102.804977,102.893356,102.917046,102.905464,102.896652,102.912903,102.958374,102.988159,102.977318,102.835876,102.885323</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>102.949997,102.650002,102.919998,102.989998,103.680000,103.349998,102.839996,103.050003,102.669998,103.320000,104.279999,104.190002,103.690002,103.360001,103.230003,103.110001,103.029999,103.400002,103.370003,103.769997,103.800003,103.449997,103.309998,103.769997</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.142349,0.332115,0.004791,0.059288,0.838669,0.493377,0.083435,0.160416,0.221352,0.479805,1.419113,1.255844,0.826767,0.555024,0.336647,0.192955,0.124535,0.503350,0.457100,0.811623,0.811844,0.472679,0.474122,0.884674</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.138270,0.323542,0.004655,0.057567,0.808902,0.477385,0.081131,0.155668,0.215595,0.464387,1.360868,1.205341,0.797345,0.536981,0.326114,0.187135,0.120872,0.486798,0.442198,0.782136,0.782123,0.456915,0.458931,0.852533</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.480141330567365</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>102.850006,103.001793,102.882187,102.953857,103.010109,102.954994,102.956055,102.803436,102.729073,102.867523,102.563370,102.826202,102.891640,102.956627,102.801498,102.794235,102.947815,102.855148,103.068649,102.852310,102.778534,102.804489,102.786896,102.882751</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>102.640640,102.470566,102.294830,102.227188,102.050247,101.932602,101.898399,101.805710,101.897102,101.667648,101.490524,101.541245,101.412605,101.248840,101.401230,101.339493,101.184113,101.120262,101.034248,101.124985,101.133041,101.002419,100.854523,100.834518</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>103.719421,103.672455,103.628731,103.710556,103.575516,103.654762,103.680702,103.640915,103.682480,103.625298,103.611725,103.703857,103.615448,103.565445,103.613747,103.583015,103.555824,103.551315,103.573418,103.585915,103.632431,103.572685,103.492523,103.556595</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>103.670174,103.643723,103.581253,103.709358,103.775391,103.690285,103.687012,103.524239,103.477554,103.597664,103.382690,103.565186,103.692932,103.885345,103.497086,103.271576,103.503258,103.574905,103.655327,103.410919,103.459625,103.277603,103.578560,103.634048</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>103.089508,103.036484,102.743439,102.840057,102.497993,102.452148,102.449478,102.244682,102.095566,101.950432,101.831314,101.769882,101.591812,101.545715,101.550949,101.512238,101.373848,101.290436,101.018806,101.022934,101.051659,101.033524,100.922256,100.893173</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>103.370941,103.236992,103.072891,103.096466,102.877762,102.836136,102.846146,102.760788,102.835388,102.646667,102.465439,102.542328,102.437012,102.268799,102.400261,102.338028,102.195435,102.119003,102.088081,102.113022,102.150803,102.012405,102.004326,102.036583</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>103.5565948486328</v>
+      </c>
+      <c r="G53" t="n">
+        <v>102.0599975585938</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.496597290039048</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.466389698059551</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.02204725501079</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:19:58</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="n">
+        <v>102.009033203125</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>103.719421,103.672455,103.628731,103.710556,103.575516,103.654762,103.680702,103.640915,103.682480,103.625298,103.611725,103.703857,103.615448,103.565445,103.613747,103.583015,103.555824,103.551315,103.573418,103.585915,103.632431,103.572685,103.492523,103.556595</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>104.080002,104.500000,104.559998,104.820000,103.500000,103.790001,104.220001,104.639999,103.779999,103.459999,103.050003,103.389999,103.519997,103.260002,102.300003,102.550003,102.080002,100.800003,101.699997,100.980003,101.029999,101.849998,101.809998,102.059998</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.360581,0.827545,0.931267,1.109444,0.075516,0.135239,0.539299,0.999084,0.097519,0.165299,0.561722,0.313858,0.095451,0.305443,1.313744,1.033012,1.475822,2.751312,1.873421,2.605912,2.602432,1.722687,1.682525,1.496597</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.346446,0.791909,0.890653,1.058427,0.072962,0.130301,0.517462,0.954782,0.093967,0.159771,0.545096,0.303567,0.092206,0.295800,1.284207,1.007325,1.445751,2.729476,1.842105,2.580621,2.575900,1.691396,1.652613,1.466390</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1.02204725501079</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>103.670174,103.643723,103.581253,103.709358,103.775391,103.690285,103.687012,103.524239,103.477554,103.597664,103.382690,103.565186,103.692932,103.885345,103.497086,103.271576,103.503258,103.574905,103.655327,103.410919,103.459625,103.277603,103.578560,103.634048</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>103.370941,103.236992,103.072891,103.096466,102.877762,102.836136,102.846146,102.760788,102.835388,102.646667,102.465439,102.542328,102.437012,102.268799,102.400261,102.338028,102.195435,102.119003,102.088081,102.113022,102.150803,102.012405,102.004326,102.036583</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:19:58</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>101.851799,101.806061,101.824265,101.870651,101.784164,101.758682,101.740829,101.717216,101.809486,101.835541,101.806366,101.917511,101.897392,101.859528,101.918167,101.936745,101.889191,101.838318,101.932114,101.908112,101.996689,101.950012,101.929207,102.009033</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>101.754219,101.844955,101.673187,101.815636,102.063309,101.808624,101.785286,101.690598,101.622368,101.827850,101.727844,101.955719,101.968506,102.008362,101.861191,101.594269,101.951103,102.010376,102.102837,101.835175,102.029137,101.570305,101.881104,102.109253</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>101.108208,100.975357,100.795937,100.809189,100.543228,100.381775,100.301567,100.180298,100.126953,100.059799,99.929260,99.829979,99.655045,99.718590,99.738953,99.717117,99.534904,99.434326,99.238068,99.185555,99.358841,99.289566,99.235931,99.206146</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>101.423981,101.230347,101.173569,101.129791,100.963226,100.816010,100.739700,100.685577,100.838913,100.722008,100.516968,100.597191,100.504089,100.423294,100.554062,100.525208,100.369667,100.245377,100.301712,100.279495,100.374603,100.274231,100.266663,100.287941</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>102.009033203125</v>
+      </c>
+      <c r="G54" t="n">
+        <v>99.43000030517578</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.579032897949219</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.593817650642176</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.851760700152305</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:43</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>99.10138702392578</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>101.851799,101.806061,101.824265,101.870651,101.784164,101.758682,101.740829,101.717216,101.809486,101.835541,101.806366,101.917511,101.897392,101.859528,101.918167,101.936745,101.889191,101.838318,101.932114,101.908112,101.996689,101.950012,101.929207,102.009033</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>102.089996,101.919998,101.290001,101.139999,101.040001,101.019997,100.980003,98.889999,99.720001,100.169998,99.699997,99.629997,99.930000,99.889999,99.629997,100.019997,99.779999,99.250000,98.610001,99.120003,99.419998,99.279999,99.279999,99.430000</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0.238197,0.113937,0.534264,0.730652,0.744163,0.738685,0.760826,2.827217,2.089485,1.665543,2.106369,2.287514,1.967392,1.969529,2.288170,1.916748,2.109192,2.588318,3.322113,2.788109,2.576691,2.670013,2.649208,2.579033</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.233321,0.111791,0.527460,0.722416,0.736503,0.731227,0.753442,2.858951,2.095352,1.662716,2.112707,2.296009,1.968770,1.971697,2.296667,1.916365,2.113843,2.607877,3.368942,2.812862,2.591723,2.689377,2.668421,2.593817</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1.851760700152305</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>101.754219,101.844955,101.673187,101.815636,102.063309,101.808624,101.785286,101.690598,101.622368,101.827850,101.727844,101.955719,101.968506,102.008362,101.861191,101.594269,101.951103,102.010376,102.102837,101.835175,102.029137,101.570305,101.881104,102.109253</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>101.423981,101.230347,101.173569,101.129791,100.963226,100.816010,100.739700,100.685577,100.838913,100.722008,100.516968,100.597191,100.504089,100.423294,100.554062,100.525208,100.369667,100.245377,100.301712,100.279495,100.374603,100.274231,100.266663,100.287941</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:43</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>99.348724,99.303902,99.380951,99.413528,99.342804,99.359604,99.307610,99.253174,99.221054,99.191162,99.112228,99.207237,99.170410,99.160385,99.217545,99.186554,99.113281,99.153793,99.148392,99.144272,99.178246,99.085548,99.071304,99.101387</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>99.323654,99.362625,99.166016,99.442734,99.558174,99.376534,99.265320,99.242416,99.227829,99.237610,99.125984,99.225281,99.179077,99.224091,99.284309,98.950867,99.201363,99.413971,99.440063,99.024170,99.325340,98.829346,99.126083,99.195618</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>98.404465,98.287483,98.151825,98.249802,98.059113,98.031693,97.986298,97.829788,97.510704,97.307800,97.188988,97.221039,97.004539,96.997864,97.077133,96.887924,96.730896,96.615669,96.364517,96.354065,96.341110,96.182785,96.156059,96.078690</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>98.848679,98.645966,98.664383,98.603226,98.558823,98.535797,98.434029,98.283737,98.368820,98.104126,97.866394,97.996094,97.880600,97.822273,98.022720,97.870102,97.670044,97.538239,97.499748,97.527580,97.511581,97.283035,97.340164,97.306534</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>99.10138702392578</v>
+      </c>
+      <c r="G55" t="n">
+        <v>101.5999984741211</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.498611450195312</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.459263275315642</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.159088594964125</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:53</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>101.2127685546875</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>99.348724,99.303902,99.380951,99.413528,99.342804,99.359604,99.307610,99.253174,99.221054,99.191162,99.112228,99.207237,99.170410,99.160385,99.217545,99.186554,99.113281,99.153793,99.148392,99.144272,99.178246,99.085548,99.071304,99.101387</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>99.870003,99.790001,99.720001,99.889999,99.389999,99.150002,99.470001,101.639999,104.790001,103.269997,101.580002,102.320000,101.940002,101.050003,102.019997,102.459999,102.070000,101.870003,102.449997,101.910004,101.980003,101.870003,101.629997,101.599998</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.521279,0.486099,0.339050,0.476471,0.047195,0.209602,0.162391,2.386825,5.568947,4.078835,2.467774,3.112763,2.769592,1.889618,2.802452,3.273445,2.956719,2.716210,3.301605,2.765732,2.801757,2.784455,2.558693,2.498611</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.521957,0.487122,0.340002,0.476996,0.047485,0.211399,0.163256,2.348313,5.314388,3.949680,2.429389,3.042184,2.716885,1.869983,2.746963,3.194852,2.896756,2.666349,3.222650,2.713896,2.747360,2.733341,2.517656,2.459263</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.159088594964125</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>99.323654,99.362625,99.166016,99.442734,99.558174,99.376534,99.265320,99.242416,99.227829,99.237610,99.125984,99.225281,99.179077,99.224091,99.284309,98.950867,99.201363,99.413971,99.440063,99.024170,99.325340,98.829346,99.126083,99.195618</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>98.848679,98.645966,98.664383,98.603226,98.558823,98.535797,98.434029,98.283737,98.368820,98.104126,97.866394,97.996094,97.880600,97.822273,98.022720,97.870102,97.670044,97.538239,97.499748,97.527580,97.511581,97.283035,97.340164,97.306534</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:53</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>101.491920,101.446304,101.501923,101.538452,101.470413,101.483307,101.483963,101.422272,101.391502,101.368286,101.375961,101.366974,101.365868,101.321869,101.419624,101.330215,101.339142,101.354439,101.316368,101.335724,101.341309,101.291931,101.159210,101.212769</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>101.501205,101.323380,101.436447,101.582092,101.580559,101.501740,101.384415,101.425232,101.341553,101.445480,101.459808,101.390213,101.219254,101.427368,101.407349,101.144073,101.386475,101.279076,101.290939,101.238297,101.306732,101.121277,101.270401,101.312614</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>100.379547,100.296112,100.181900,100.251007,99.982666,99.918541,99.835533,99.620529,99.476631,99.371979,99.384575,99.266685,99.137421,99.070389,99.195229,98.951370,98.918686,98.830452,98.528046,98.469025,98.538681,98.398178,98.312851,98.232468</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>100.863075,100.683830,100.658966,100.654343,100.527344,100.432709,100.395866,100.281731,100.327148,100.154861,100.090981,100.099724,100.011108,99.879738,100.116409,99.888382,99.825989,99.707108,99.626656,99.631973,99.668816,99.486633,99.403824,99.386078</t>
         </is>
       </c>
     </row>
